--- a/code_introduction.xlsx
+++ b/code_introduction.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EJ-User03\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pycharm Project\2EH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11B2AD6B-4334-436A-8849-C0D0B1BA45A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D6E13B-13AF-405D-9A34-6E2C793FBCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{F88859C5-A072-4064-BA9E-C15A92D606DA}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" activeTab="5" xr2:uid="{F88859C5-A072-4064-BA9E-C15A92D606DA}"/>
   </bookViews>
   <sheets>
     <sheet name="dim_reduce" sheetId="1" r:id="rId1"/>
-    <sheet name="plot_figure" sheetId="2" r:id="rId2"/>
-    <sheet name="regression" sheetId="3" r:id="rId3"/>
-    <sheet name="Utilities" sheetId="4" r:id="rId4"/>
+    <sheet name="nn_plot_figure" sheetId="5" r:id="rId2"/>
+    <sheet name="nn_regression" sheetId="6" r:id="rId3"/>
+    <sheet name="plot_figure" sheetId="7" r:id="rId4"/>
+    <sheet name="regression" sheetId="9" r:id="rId5"/>
+    <sheet name="Utilities" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="205">
   <si>
     <t>降維統計方法</t>
   </si>
@@ -207,13 +209,500 @@
   </si>
   <si>
     <t>UMAP投影完潛空間</t>
+  </si>
+  <si>
+    <t>seq2seq_plot</t>
+  </si>
+  <si>
+    <t>plot_loss</t>
+  </si>
+  <si>
+    <t>history</t>
+  </si>
+  <si>
+    <t>神經網路訓練歷史資料</t>
+  </si>
+  <si>
+    <t>畫每一步的loss</t>
+  </si>
+  <si>
+    <t>seq2seq</t>
+  </si>
+  <si>
+    <t>seq2seq_model</t>
+  </si>
+  <si>
+    <t>訓練S2S model</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>x_hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y_hidden </t>
+  </si>
+  <si>
+    <t xml:space="preserve">batch_size </t>
+  </si>
+  <si>
+    <t xml:space="preserve">verbose </t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>epochs</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>encoder 神經元</t>
+  </si>
+  <si>
+    <t>decoder 神經元</t>
+  </si>
+  <si>
+    <t>一個batch 幾筆參數</t>
+  </si>
+  <si>
+    <t>訓練步數</t>
+  </si>
+  <si>
+    <t>是否顯示</t>
+  </si>
+  <si>
+    <t>seq2seq 模型</t>
+  </si>
+  <si>
+    <t>歷史訓練loss</t>
+  </si>
+  <si>
+    <t>labels</t>
+  </si>
+  <si>
+    <t>plot_samping</t>
+  </si>
+  <si>
+    <t>general_plot</t>
+  </si>
+  <si>
+    <t>general_plot_2D</t>
+  </si>
+  <si>
+    <t>general_plot_2D_color</t>
+  </si>
+  <si>
+    <t>general_plot_3D</t>
+  </si>
+  <si>
+    <t>general_plot_3D_color</t>
+  </si>
+  <si>
+    <t>通用畫2D圖(可根據"群"標記)</t>
+  </si>
+  <si>
+    <t>通用畫3D圖(可根據"群"標記)</t>
+  </si>
+  <si>
+    <t>通用畫2D圖(根據時間序漸層)</t>
+  </si>
+  <si>
+    <t>通用畫3D圖(根據時間序漸層)</t>
+  </si>
+  <si>
+    <t>標籤</t>
+  </si>
+  <si>
+    <t>是否標時間順序</t>
+  </si>
+  <si>
+    <t>pca_plot_2D</t>
+  </si>
+  <si>
+    <t>pca_vactor</t>
+  </si>
+  <si>
+    <t>pca_varience_ratio</t>
+  </si>
+  <si>
+    <t>figure_name</t>
+  </si>
+  <si>
+    <t>PCA畫2D圖(可根據"群"標記)
+存.png</t>
+  </si>
+  <si>
+    <t>pca_plot_2D_html</t>
+  </si>
+  <si>
+    <t>pca_plot_3D</t>
+  </si>
+  <si>
+    <t>pca_plot_3D_html</t>
+  </si>
+  <si>
+    <t>pca_plot_2D_color</t>
+  </si>
+  <si>
+    <t>pca_plot_2D_color_html</t>
+  </si>
+  <si>
+    <t>pca_plot_3D_color</t>
+  </si>
+  <si>
+    <t>pca_plot_3D_color_html</t>
+  </si>
+  <si>
+    <t>pca_plot_2D_variable_vector</t>
+  </si>
+  <si>
+    <t>pca_plot_2D_variable_vector_html</t>
+  </si>
+  <si>
+    <t>pca_plot_3D_variable_vector_html</t>
+  </si>
+  <si>
+    <t>PCA 方向線</t>
+  </si>
+  <si>
+    <t>PCA 變異量比例</t>
+  </si>
+  <si>
+    <t>標示時間順序間隔</t>
+  </si>
+  <si>
+    <t>圖名</t>
+  </si>
+  <si>
+    <t>PCA畫2D圖(可根據"群"標記)
+存.html</t>
+  </si>
+  <si>
+    <t>PCA畫3D圖(可根據"群"標記)
+存.png</t>
+  </si>
+  <si>
+    <t>PCA畫3D圖(可根據"群"標記)
+存.html</t>
+  </si>
+  <si>
+    <t>PCA畫2D圖(根據時間序漸層)
+存.png</t>
+  </si>
+  <si>
+    <t>PCA畫2D圖(根據時間序漸層)
+存.html</t>
+  </si>
+  <si>
+    <t>PCA畫3D圖(根據時間序漸層)
+存.png</t>
+  </si>
+  <si>
+    <t>PCA畫3D圖(根據時間序漸層)
+存.html</t>
+  </si>
+  <si>
+    <t>vector_name</t>
+  </si>
+  <si>
+    <t>變量名稱</t>
+  </si>
+  <si>
+    <t>畫PCA個變量重要性
+存.png</t>
+  </si>
+  <si>
+    <t>畫PCA個變量重要性
+存.html</t>
+  </si>
+  <si>
+    <t>PCA_plot</t>
+  </si>
+  <si>
+    <t>tsne_plot_2D</t>
+  </si>
+  <si>
+    <t>tsne_plot_2D_html</t>
+  </si>
+  <si>
+    <t>tsne_plot_2D_color</t>
+  </si>
+  <si>
+    <t>tsne_plot_2D_color_html</t>
+  </si>
+  <si>
+    <t>tsne_plot_3D</t>
+  </si>
+  <si>
+    <t>tsne_plot_3D_html</t>
+  </si>
+  <si>
+    <t>tsne_plot_3D_color</t>
+  </si>
+  <si>
+    <t>tsne_plot_3D_color_html</t>
+  </si>
+  <si>
+    <t>T-SNE 畫2D
+存.png</t>
+  </si>
+  <si>
+    <t>T-SNE畫2D圖(根據時間序漸層)
+存.png</t>
+  </si>
+  <si>
+    <t>T-SNE 畫2D
+存.html</t>
+  </si>
+  <si>
+    <t>T-SNE畫2D圖(根據時間序漸層)
+存.html</t>
+  </si>
+  <si>
+    <t>T-SNE 畫3D
+存.png</t>
+  </si>
+  <si>
+    <t>T-SNE 畫3D
+存.html</t>
+  </si>
+  <si>
+    <t>T-SNE畫3D圖(根據時間序漸層)
+存.png</t>
+  </si>
+  <si>
+    <t>T-SNE畫3D圖(根據時間序漸層)
+存.html</t>
+  </si>
+  <si>
+    <t>TSNE_plot</t>
+  </si>
+  <si>
+    <t>umap_plot_2D</t>
+  </si>
+  <si>
+    <t>umap_plot_2D_html</t>
+  </si>
+  <si>
+    <t>umap_plot_2D_color</t>
+  </si>
+  <si>
+    <t>umap_plot_2D_color_html</t>
+  </si>
+  <si>
+    <t>umap_plot_3D</t>
+  </si>
+  <si>
+    <t>umap_plot_3D_html</t>
+  </si>
+  <si>
+    <t>umap_plot_3D_color</t>
+  </si>
+  <si>
+    <t>umap_plot_3D_color_html</t>
+  </si>
+  <si>
+    <t>UMAP_plot</t>
+  </si>
+  <si>
+    <t>UMAP 畫2D
+存.png</t>
+  </si>
+  <si>
+    <t>UMAP 畫2D
+存.html</t>
+  </si>
+  <si>
+    <t>UMAP畫2D圖(根據時間序漸層)
+存.png</t>
+  </si>
+  <si>
+    <t>UMAP畫2D圖(根據時間序漸層)
+存.html</t>
+  </si>
+  <si>
+    <t>UMAP 畫3D
+存.png</t>
+  </si>
+  <si>
+    <t>UMAP 畫3D
+存.html</t>
+  </si>
+  <si>
+    <t>UMAP畫3D圖(根據時間序漸層)
+存.png</t>
+  </si>
+  <si>
+    <t>UMAP畫3D圖(根據時間序漸層)
+存.html</t>
+  </si>
+  <si>
+    <t>interval_sampling</t>
+  </si>
+  <si>
+    <t>expand_timeseries</t>
+  </si>
+  <si>
+    <t>time_sampling</t>
+  </si>
+  <si>
+    <t>detect_time_interval</t>
+  </si>
+  <si>
+    <t>normalize_gaussian</t>
+  </si>
+  <si>
+    <t>multi_interval_sampling</t>
+  </si>
+  <si>
+    <t>multi_time_sampling</t>
+  </si>
+  <si>
+    <t>sort_3D_data</t>
+  </si>
+  <si>
+    <t>multi_sort_3D_data</t>
+  </si>
+  <si>
+    <t>merge_with_gap</t>
+  </si>
+  <si>
+    <t>find_nan_data</t>
+  </si>
+  <si>
+    <t>start_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end_index </t>
+  </si>
+  <si>
+    <t>interval_count</t>
+  </si>
+  <si>
+    <t>interval_data</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>time_index</t>
+  </si>
+  <si>
+    <t>data_new</t>
+  </si>
+  <si>
+    <t>start_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end_time </t>
+  </si>
+  <si>
+    <t>time_low</t>
+  </si>
+  <si>
+    <t>series</t>
+  </si>
+  <si>
+    <r>
+      <t>f"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color theme="1"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>{nearest_minute*60}s"</t>
+    </r>
+  </si>
+  <si>
+    <t>normalize_data</t>
+  </si>
+  <si>
+    <t>mean_data</t>
+  </si>
+  <si>
+    <t>std_data</t>
+  </si>
+  <si>
+    <t>start_time_list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end_time_list </t>
+  </si>
+  <si>
+    <t>data_lengths</t>
+  </si>
+  <si>
+    <t>intput_index</t>
+  </si>
+  <si>
+    <t>output_index</t>
+  </si>
+  <si>
+    <t>input_index</t>
+  </si>
+  <si>
+    <t>input_time_step</t>
+  </si>
+  <si>
+    <t>output_time_step</t>
+  </si>
+  <si>
+    <t>jump_step</t>
+  </si>
+  <si>
+    <t>all_x</t>
+  </si>
+  <si>
+    <t>all_y</t>
+  </si>
+  <si>
+    <t>data_x_3D</t>
+  </si>
+  <si>
+    <t>data_y_3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data </t>
+  </si>
+  <si>
+    <t>out_put_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output_time_step </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jump_step </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rows </t>
+  </si>
+  <si>
+    <t>max_gap</t>
+  </si>
+  <si>
+    <t>ranges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time_index </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -221,6 +710,12 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color theme="1"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -295,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -306,10 +801,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -324,7 +849,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -662,371 +1190,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEEA317E-42C0-4A1C-B89C-A4DFF7728AEA}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="16.09765625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.59765625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.296875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="27.8984375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="36.69921875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.09765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.8984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="36.69921875" style="3" customWidth="1"/>
     <col min="7" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="4" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="7" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="4" t="s">
+    <row r="6" spans="1:10">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="4" t="s">
+    <row r="7" spans="1:10">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="4" t="s">
+    <row r="8" spans="1:10">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="4" t="s">
+    <row r="9" spans="1:10">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:10">
+      <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="4" t="s">
+    <row r="11" spans="1:10">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="4" t="s">
+    <row r="12" spans="1:10">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="4" t="s">
+    <row r="13" spans="1:10">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="4" t="s">
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="4" t="s">
+    <row r="15" spans="1:10">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="4" t="s">
+    <row r="16" spans="1:10">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="4" t="s">
+    <row r="17" spans="1:6">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="4" t="s">
+    <row r="18" spans="1:6">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="4" t="s">
+    <row r="19" spans="1:6">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:6">
+      <c r="A20" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="D20" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="4" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="4" t="s">
+    <row r="22" spans="1:6">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="4" t="s">
+    <row r="23" spans="1:6">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="4" t="s">
+    <row r="24" spans="1:6">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="4" t="s">
+    <row r="25" spans="1:6">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="4" t="s">
+    <row r="26" spans="1:6">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="D10:D18"/>
     <mergeCell ref="C10:C19"/>
     <mergeCell ref="A10:A19"/>
     <mergeCell ref="B10:B19"/>
@@ -1034,13 +1569,6 @@
     <mergeCell ref="C20:C26"/>
     <mergeCell ref="B20:B26"/>
     <mergeCell ref="A20:A26"/>
-    <mergeCell ref="D5:D9"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1048,28 +1576,3043 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDABD40D-45C7-48DD-9A1D-5CB072AAD54B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC4960A-CE3B-4220-A191-79F6E5A99BCE}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999"/>
+  <cols>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.09765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.8984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="36.69921875" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="11" customFormat="1">
+      <c r="A3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="D14" s="10"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E58B5EF-F905-4BE3-A92A-AA73DDC1293E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02DA657D-8434-47D4-BEC1-50E00A04EA70}">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999"/>
+  <cols>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.09765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.8984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="36.69921875" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D3:D9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C11FDB-BCDD-4203-9B02-46A98906F98C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1864DFD3-8A4E-4D94-AFAC-AC3B4B5A915B}">
+  <dimension ref="A1:J123"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999"/>
+  <cols>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.3984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.8984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="36.69921875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.59765625" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="8.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="18"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="18"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="18"/>
+      <c r="B6" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="18"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="18"/>
+      <c r="B8" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="18"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="18"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="18"/>
+      <c r="B11" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="18"/>
+      <c r="B19" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="18"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="18"/>
+      <c r="B25" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="18"/>
+      <c r="B31" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="18"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="16.149999999999999" customHeight="1">
+      <c r="A37" s="18"/>
+      <c r="B37" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="18"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="18"/>
+      <c r="B42" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="18"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="18"/>
+      <c r="B47" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="18"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="18"/>
+      <c r="B52" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="18"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="18"/>
+      <c r="B57" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="18"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="18"/>
+      <c r="B60" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="18"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="18"/>
+      <c r="B64" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="19"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="18"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="18"/>
+      <c r="B72" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="18"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="16.149999999999999" customHeight="1">
+      <c r="A76" s="18"/>
+      <c r="B76" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="18"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="18"/>
+      <c r="B79" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="18"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="18"/>
+      <c r="B82" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="18"/>
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="18"/>
+      <c r="B86" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="18"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="18"/>
+      <c r="B90" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="18"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="18"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="19"/>
+      <c r="E92" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="18"/>
+      <c r="B93" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="18"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="19"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D96" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="18"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="18"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="18"/>
+      <c r="B99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="19"/>
+      <c r="E99" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="18"/>
+      <c r="B100" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="18"/>
+      <c r="B101" s="18"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="18"/>
+      <c r="B102" s="18"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="18"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="19"/>
+      <c r="D103" s="19"/>
+      <c r="E103" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="18"/>
+      <c r="B104" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="18"/>
+      <c r="B105" s="18"/>
+      <c r="C105" s="15"/>
+      <c r="D105" s="18"/>
+      <c r="E105" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="18"/>
+      <c r="B106" s="19"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="19"/>
+      <c r="E106" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="18"/>
+      <c r="B107" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D107" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="18"/>
+      <c r="B108" s="18"/>
+      <c r="C108" s="15"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="18"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="15"/>
+      <c r="D109" s="19"/>
+      <c r="E109" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="18"/>
+      <c r="B110" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D110" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="18"/>
+      <c r="B111" s="18"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="18"/>
+      <c r="B112" s="18"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F112" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="18"/>
+      <c r="B113" s="19"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="19"/>
+      <c r="E113" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="18"/>
+      <c r="B114" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D114" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="18"/>
+      <c r="B115" s="18"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="18"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F116" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="18"/>
+      <c r="B117" s="19"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="18"/>
+      <c r="B118" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C118" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D118" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="18"/>
+      <c r="B119" s="18"/>
+      <c r="C119" s="15"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="18"/>
+      <c r="B120" s="19"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="19"/>
+      <c r="E120" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="18"/>
+      <c r="B121" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C121" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D121" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="18"/>
+      <c r="B122" s="18"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="18"/>
+      <c r="E122" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F122" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="19"/>
+      <c r="B123" s="19"/>
+      <c r="C123" s="15"/>
+      <c r="D123" s="19"/>
+      <c r="E123" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="98">
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D121:D123"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="A68:A95"/>
+    <mergeCell ref="A96:A123"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="D104:D106"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="D90:D92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="D79:D81"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="A13:A67"/>
+    <mergeCell ref="D68:D71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="D47:D51"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="D52:D56"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="D31:D36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="D19:D24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="D25:D30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D13:D18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F915460F-6392-40BC-9A12-9B3DBF323C60}">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999"/>
+  <cols>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.09765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.8984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="36.69921875" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89F3D3C-6CDD-4026-851E-F3F25E51AE26}">
+  <dimension ref="A1:J58"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999"/>
+  <cols>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.296875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="27.8984375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="36.69921875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="24.296875" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="8.796875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="8"/>
+      <c r="B3" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="8"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="8"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="8"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="8"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="8"/>
+      <c r="B8" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="8"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="8"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="8"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="8"/>
+      <c r="B12" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="8"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="8"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="8"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="8"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="8"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="8"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="8"/>
+      <c r="B19" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="8"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="8"/>
+      <c r="B21" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="8"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="8"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="8"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="8"/>
+      <c r="B25" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="8"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="C55:C58"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="D43:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="C43:C51"/>
+    <mergeCell ref="B43:B51"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="D35:D40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C35:C42"/>
+    <mergeCell ref="B35:B42"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D27:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C27:C34"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="D12:D17"/>
+    <mergeCell ref="C12:C18"/>
+    <mergeCell ref="B12:B18"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/code_introduction.xlsx
+++ b/code_introduction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pycharm Project\2EH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D6E13B-13AF-405D-9A34-6E2C793FBCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1368C001-AF09-419C-BEC4-5D8FD5E85247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" activeTab="5" xr2:uid="{F88859C5-A072-4064-BA9E-C15A92D606DA}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="206">
   <si>
     <t>降維統計方法</t>
   </si>
@@ -696,6 +696,9 @@
   </si>
   <si>
     <t xml:space="preserve">time_index </t>
+  </si>
+  <si>
+    <t>preprocessing</t>
   </si>
 </sst>
 </file>
@@ -831,10 +834,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -849,8 +852,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1202,14 +1205,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1245,7 +1248,7 @@
       <c r="C3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1339,7 +1342,7 @@
       <c r="C10" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1353,7 +1356,7 @@
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
-      <c r="D11" s="15"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
@@ -1365,7 +1368,7 @@
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
-      <c r="D12" s="15"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1377,7 +1380,7 @@
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
-      <c r="D13" s="15"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
@@ -1389,7 +1392,7 @@
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
-      <c r="D14" s="15"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="3" t="s">
         <v>31</v>
       </c>
@@ -1401,7 +1404,7 @@
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
-      <c r="D15" s="15"/>
+      <c r="D15" s="20"/>
       <c r="E15" s="3" t="s">
         <v>32</v>
       </c>
@@ -1413,7 +1416,7 @@
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="15"/>
+      <c r="D16" s="20"/>
       <c r="E16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1425,7 +1428,7 @@
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
-      <c r="D17" s="15"/>
+      <c r="D17" s="20"/>
       <c r="E17" s="3" t="s">
         <v>34</v>
       </c>
@@ -1555,12 +1558,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D9"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="A3:A9"/>
     <mergeCell ref="D10:D18"/>
     <mergeCell ref="C10:C19"/>
     <mergeCell ref="A10:A19"/>
@@ -1569,6 +1566,12 @@
     <mergeCell ref="C20:C26"/>
     <mergeCell ref="B20:B26"/>
     <mergeCell ref="A20:A26"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="A3:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1590,14 +1593,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
@@ -1733,14 +1736,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1776,7 +1779,7 @@
       <c r="C3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1790,7 +1793,7 @@
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
-      <c r="D4" s="15"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="3" t="s">
         <v>64</v>
       </c>
@@ -1802,7 +1805,7 @@
       <c r="A5" s="18"/>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
-      <c r="D5" s="15"/>
+      <c r="D5" s="20"/>
       <c r="E5" s="3" t="s">
         <v>65</v>
       </c>
@@ -1814,7 +1817,7 @@
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
-      <c r="D6" s="15"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
@@ -1826,7 +1829,7 @@
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
-      <c r="D7" s="15"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="3" t="s">
         <v>67</v>
       </c>
@@ -1838,7 +1841,7 @@
       <c r="A8" s="18"/>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
-      <c r="D8" s="15"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="3" t="s">
         <v>70</v>
       </c>
@@ -2002,14 +2005,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -2038,10 +2041,10 @@
       <c r="A3" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="14" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="21" t="s">
@@ -2056,8 +2059,8 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="18"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="21"/>
       <c r="E4" s="3" t="s">
         <v>80</v>
@@ -2068,8 +2071,8 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="18"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
       <c r="D5" s="21"/>
       <c r="E5" s="3" t="s">
         <v>81</v>
@@ -2080,13 +2083,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="18"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="14" t="s">
         <v>84</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -2098,7 +2101,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="18"/>
-      <c r="B7" s="20"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="19"/>
       <c r="D7" s="16"/>
       <c r="E7" s="7" t="s">
@@ -2110,13 +2113,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="18"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -2128,9 +2131,9 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="18"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="7" t="s">
         <v>80</v>
       </c>
@@ -2140,8 +2143,8 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="18"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="16"/>
       <c r="E10" s="7" t="s">
         <v>81</v>
@@ -2152,13 +2155,13 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="18"/>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="14" t="s">
         <v>86</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -2170,7 +2173,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="19"/>
       <c r="D12" s="16"/>
       <c r="E12" s="7" t="s">
@@ -2187,10 +2190,10 @@
       <c r="B13" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -2204,7 +2207,7 @@
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
-      <c r="D14" s="15"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="3" t="s">
         <v>94</v>
       </c>
@@ -2216,7 +2219,7 @@
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
-      <c r="D15" s="15"/>
+      <c r="D15" s="20"/>
       <c r="E15" s="3" t="s">
         <v>95</v>
       </c>
@@ -2228,7 +2231,7 @@
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="15"/>
+      <c r="D16" s="20"/>
       <c r="E16" s="3" t="s">
         <v>80</v>
       </c>
@@ -2240,7 +2243,7 @@
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
-      <c r="D17" s="15"/>
+      <c r="D17" s="20"/>
       <c r="E17" s="12" t="s">
         <v>81</v>
       </c>
@@ -2265,10 +2268,10 @@
       <c r="B19" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -2282,7 +2285,7 @@
       <c r="A20" s="18"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
-      <c r="D20" s="15"/>
+      <c r="D20" s="20"/>
       <c r="E20" s="12" t="s">
         <v>94</v>
       </c>
@@ -2294,7 +2297,7 @@
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
-      <c r="D21" s="15"/>
+      <c r="D21" s="20"/>
       <c r="E21" s="12" t="s">
         <v>95</v>
       </c>
@@ -2306,7 +2309,7 @@
       <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
-      <c r="D22" s="15"/>
+      <c r="D22" s="20"/>
       <c r="E22" s="12" t="s">
         <v>80</v>
       </c>
@@ -2318,7 +2321,7 @@
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
-      <c r="D23" s="15"/>
+      <c r="D23" s="20"/>
       <c r="E23" s="12" t="s">
         <v>81</v>
       </c>
@@ -2343,10 +2346,10 @@
       <c r="B25" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -2360,7 +2363,7 @@
       <c r="A26" s="18"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
-      <c r="D26" s="15"/>
+      <c r="D26" s="20"/>
       <c r="E26" s="12" t="s">
         <v>94</v>
       </c>
@@ -2372,7 +2375,7 @@
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
-      <c r="D27" s="15"/>
+      <c r="D27" s="20"/>
       <c r="E27" s="12" t="s">
         <v>95</v>
       </c>
@@ -2384,7 +2387,7 @@
       <c r="A28" s="18"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
-      <c r="D28" s="15"/>
+      <c r="D28" s="20"/>
       <c r="E28" s="12" t="s">
         <v>80</v>
       </c>
@@ -2396,7 +2399,7 @@
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
-      <c r="D29" s="15"/>
+      <c r="D29" s="20"/>
       <c r="E29" s="12" t="s">
         <v>81</v>
       </c>
@@ -2421,10 +2424,10 @@
       <c r="B31" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -2438,7 +2441,7 @@
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
-      <c r="D32" s="15"/>
+      <c r="D32" s="20"/>
       <c r="E32" s="12" t="s">
         <v>94</v>
       </c>
@@ -2450,7 +2453,7 @@
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
-      <c r="D33" s="15"/>
+      <c r="D33" s="20"/>
       <c r="E33" s="12" t="s">
         <v>95</v>
       </c>
@@ -2462,7 +2465,7 @@
       <c r="A34" s="18"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
-      <c r="D34" s="15"/>
+      <c r="D34" s="20"/>
       <c r="E34" s="12" t="s">
         <v>80</v>
       </c>
@@ -2474,7 +2477,7 @@
       <c r="A35" s="18"/>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="15"/>
+      <c r="D35" s="20"/>
       <c r="E35" s="12" t="s">
         <v>81</v>
       </c>
@@ -2499,10 +2502,10 @@
       <c r="B37" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -2515,8 +2518,8 @@
     <row r="38" spans="1:6">
       <c r="A38" s="18"/>
       <c r="B38" s="18"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
       <c r="E38" s="12" t="s">
         <v>94</v>
       </c>
@@ -2527,8 +2530,8 @@
     <row r="39" spans="1:6">
       <c r="A39" s="18"/>
       <c r="B39" s="18"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
       <c r="E39" s="12" t="s">
         <v>95</v>
       </c>
@@ -2539,8 +2542,8 @@
     <row r="40" spans="1:6">
       <c r="A40" s="18"/>
       <c r="B40" s="18"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
       <c r="E40" s="12" t="s">
         <v>81</v>
       </c>
@@ -2565,10 +2568,10 @@
       <c r="B42" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -2581,8 +2584,8 @@
     <row r="43" spans="1:6">
       <c r="A43" s="18"/>
       <c r="B43" s="18"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
       <c r="E43" s="12" t="s">
         <v>94</v>
       </c>
@@ -2593,8 +2596,8 @@
     <row r="44" spans="1:6">
       <c r="A44" s="18"/>
       <c r="B44" s="18"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
       <c r="E44" s="12" t="s">
         <v>95</v>
       </c>
@@ -2605,8 +2608,8 @@
     <row r="45" spans="1:6">
       <c r="A45" s="18"/>
       <c r="B45" s="18"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
       <c r="E45" s="12" t="s">
         <v>81</v>
       </c>
@@ -2631,10 +2634,10 @@
       <c r="B47" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -2647,8 +2650,8 @@
     <row r="48" spans="1:6">
       <c r="A48" s="18"/>
       <c r="B48" s="18"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
       <c r="E48" s="12" t="s">
         <v>94</v>
       </c>
@@ -2659,8 +2662,8 @@
     <row r="49" spans="1:6">
       <c r="A49" s="18"/>
       <c r="B49" s="18"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
       <c r="E49" s="12" t="s">
         <v>95</v>
       </c>
@@ -2671,8 +2674,8 @@
     <row r="50" spans="1:6">
       <c r="A50" s="18"/>
       <c r="B50" s="18"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
       <c r="E50" s="12" t="s">
         <v>81</v>
       </c>
@@ -2697,10 +2700,10 @@
       <c r="B52" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -2713,8 +2716,8 @@
     <row r="53" spans="1:6">
       <c r="A53" s="18"/>
       <c r="B53" s="18"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
       <c r="E53" s="12" t="s">
         <v>94</v>
       </c>
@@ -2725,8 +2728,8 @@
     <row r="54" spans="1:6">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
       <c r="E54" s="12" t="s">
         <v>95</v>
       </c>
@@ -2737,8 +2740,8 @@
     <row r="55" spans="1:6">
       <c r="A55" s="18"/>
       <c r="B55" s="18"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
       <c r="E55" s="12" t="s">
         <v>81</v>
       </c>
@@ -2763,7 +2766,7 @@
       <c r="B57" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="15" t="s">
         <v>121</v>
       </c>
       <c r="D57" s="17" t="s">
@@ -2805,7 +2808,7 @@
       <c r="B60" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="15" t="s">
         <v>122</v>
       </c>
       <c r="D60" s="17" t="s">
@@ -2859,7 +2862,7 @@
       <c r="B64" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="15" t="s">
         <v>122</v>
       </c>
       <c r="D64" s="17" t="s">
@@ -2915,7 +2918,7 @@
       <c r="B68" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="15" t="s">
         <v>132</v>
       </c>
       <c r="D68" s="17" t="s">
@@ -2969,7 +2972,7 @@
       <c r="B72" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="15" t="s">
         <v>134</v>
       </c>
       <c r="D72" s="17" t="s">
@@ -3023,7 +3026,7 @@
       <c r="B76" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="15" t="s">
         <v>133</v>
       </c>
       <c r="D76" s="17" t="s">
@@ -3039,7 +3042,7 @@
     <row r="77" spans="1:6">
       <c r="A77" s="18"/>
       <c r="B77" s="18"/>
-      <c r="C77" s="15"/>
+      <c r="C77" s="20"/>
       <c r="D77" s="18"/>
       <c r="E77" s="12" t="s">
         <v>81</v>
@@ -3051,7 +3054,7 @@
     <row r="78" spans="1:6">
       <c r="A78" s="18"/>
       <c r="B78" s="19"/>
-      <c r="C78" s="15"/>
+      <c r="C78" s="20"/>
       <c r="D78" s="19"/>
       <c r="E78" s="12" t="s">
         <v>96</v>
@@ -3065,7 +3068,7 @@
       <c r="B79" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="15" t="s">
         <v>135</v>
       </c>
       <c r="D79" s="17" t="s">
@@ -3081,7 +3084,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="18"/>
       <c r="B80" s="18"/>
-      <c r="C80" s="15"/>
+      <c r="C80" s="20"/>
       <c r="D80" s="18"/>
       <c r="E80" s="12" t="s">
         <v>81</v>
@@ -3093,7 +3096,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="18"/>
       <c r="B81" s="19"/>
-      <c r="C81" s="15"/>
+      <c r="C81" s="20"/>
       <c r="D81" s="19"/>
       <c r="E81" s="12" t="s">
         <v>96</v>
@@ -3107,7 +3110,7 @@
       <c r="B82" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="15" t="s">
         <v>136</v>
       </c>
       <c r="D82" s="17" t="s">
@@ -3161,7 +3164,7 @@
       <c r="B86" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="15" t="s">
         <v>137</v>
       </c>
       <c r="D86" s="17" t="s">
@@ -3215,7 +3218,7 @@
       <c r="B90" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="15" t="s">
         <v>138</v>
       </c>
       <c r="D90" s="17" t="s">
@@ -3231,7 +3234,7 @@
     <row r="91" spans="1:6">
       <c r="A91" s="18"/>
       <c r="B91" s="18"/>
-      <c r="C91" s="15"/>
+      <c r="C91" s="20"/>
       <c r="D91" s="18"/>
       <c r="E91" s="12" t="s">
         <v>81</v>
@@ -3243,7 +3246,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="18"/>
       <c r="B92" s="19"/>
-      <c r="C92" s="15"/>
+      <c r="C92" s="20"/>
       <c r="D92" s="19"/>
       <c r="E92" s="12" t="s">
         <v>96</v>
@@ -3257,7 +3260,7 @@
       <c r="B93" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="15" t="s">
         <v>139</v>
       </c>
       <c r="D93" s="17" t="s">
@@ -3273,7 +3276,7 @@
     <row r="94" spans="1:6">
       <c r="A94" s="18"/>
       <c r="B94" s="18"/>
-      <c r="C94" s="15"/>
+      <c r="C94" s="20"/>
       <c r="D94" s="18"/>
       <c r="E94" s="12" t="s">
         <v>81</v>
@@ -3285,7 +3288,7 @@
     <row r="95" spans="1:6">
       <c r="A95" s="19"/>
       <c r="B95" s="19"/>
-      <c r="C95" s="15"/>
+      <c r="C95" s="20"/>
       <c r="D95" s="19"/>
       <c r="E95" s="12" t="s">
         <v>96</v>
@@ -3301,7 +3304,7 @@
       <c r="B96" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="15" t="s">
         <v>150</v>
       </c>
       <c r="D96" s="17" t="s">
@@ -3355,7 +3358,7 @@
       <c r="B100" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C100" s="14" t="s">
+      <c r="C100" s="15" t="s">
         <v>151</v>
       </c>
       <c r="D100" s="17" t="s">
@@ -3409,7 +3412,7 @@
       <c r="B104" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C104" s="14" t="s">
+      <c r="C104" s="15" t="s">
         <v>152</v>
       </c>
       <c r="D104" s="17" t="s">
@@ -3425,7 +3428,7 @@
     <row r="105" spans="1:6">
       <c r="A105" s="18"/>
       <c r="B105" s="18"/>
-      <c r="C105" s="15"/>
+      <c r="C105" s="20"/>
       <c r="D105" s="18"/>
       <c r="E105" s="12" t="s">
         <v>81</v>
@@ -3437,7 +3440,7 @@
     <row r="106" spans="1:6">
       <c r="A106" s="18"/>
       <c r="B106" s="19"/>
-      <c r="C106" s="15"/>
+      <c r="C106" s="20"/>
       <c r="D106" s="19"/>
       <c r="E106" s="12" t="s">
         <v>96</v>
@@ -3451,7 +3454,7 @@
       <c r="B107" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C107" s="14" t="s">
+      <c r="C107" s="15" t="s">
         <v>153</v>
       </c>
       <c r="D107" s="17" t="s">
@@ -3467,7 +3470,7 @@
     <row r="108" spans="1:6">
       <c r="A108" s="18"/>
       <c r="B108" s="18"/>
-      <c r="C108" s="15"/>
+      <c r="C108" s="20"/>
       <c r="D108" s="18"/>
       <c r="E108" s="12" t="s">
         <v>81</v>
@@ -3479,7 +3482,7 @@
     <row r="109" spans="1:6">
       <c r="A109" s="18"/>
       <c r="B109" s="19"/>
-      <c r="C109" s="15"/>
+      <c r="C109" s="20"/>
       <c r="D109" s="19"/>
       <c r="E109" s="12" t="s">
         <v>96</v>
@@ -3493,7 +3496,7 @@
       <c r="B110" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C110" s="15" t="s">
         <v>154</v>
       </c>
       <c r="D110" s="17" t="s">
@@ -3547,7 +3550,7 @@
       <c r="B114" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C114" s="14" t="s">
+      <c r="C114" s="15" t="s">
         <v>155</v>
       </c>
       <c r="D114" s="17" t="s">
@@ -3601,7 +3604,7 @@
       <c r="B118" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C118" s="14" t="s">
+      <c r="C118" s="15" t="s">
         <v>156</v>
       </c>
       <c r="D118" s="17" t="s">
@@ -3617,7 +3620,7 @@
     <row r="119" spans="1:6">
       <c r="A119" s="18"/>
       <c r="B119" s="18"/>
-      <c r="C119" s="15"/>
+      <c r="C119" s="20"/>
       <c r="D119" s="18"/>
       <c r="E119" s="12" t="s">
         <v>81</v>
@@ -3629,7 +3632,7 @@
     <row r="120" spans="1:6">
       <c r="A120" s="18"/>
       <c r="B120" s="19"/>
-      <c r="C120" s="15"/>
+      <c r="C120" s="20"/>
       <c r="D120" s="19"/>
       <c r="E120" s="12" t="s">
         <v>96</v>
@@ -3643,7 +3646,7 @@
       <c r="B121" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C121" s="14" t="s">
+      <c r="C121" s="15" t="s">
         <v>157</v>
       </c>
       <c r="D121" s="17" t="s">
@@ -3659,7 +3662,7 @@
     <row r="122" spans="1:6">
       <c r="A122" s="18"/>
       <c r="B122" s="18"/>
-      <c r="C122" s="15"/>
+      <c r="C122" s="20"/>
       <c r="D122" s="18"/>
       <c r="E122" s="12" t="s">
         <v>81</v>
@@ -3671,7 +3674,7 @@
     <row r="123" spans="1:6">
       <c r="A123" s="19"/>
       <c r="B123" s="19"/>
-      <c r="C123" s="15"/>
+      <c r="C123" s="20"/>
       <c r="D123" s="19"/>
       <c r="E123" s="12" t="s">
         <v>96</v>
@@ -3682,19 +3685,75 @@
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="D121:D123"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D13:D18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="D31:D36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="D19:D24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="D25:D30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="D52:D56"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="A13:A67"/>
+    <mergeCell ref="D68:D71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="D47:D51"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="D79:D81"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="D90:D92"/>
+    <mergeCell ref="B90:B92"/>
     <mergeCell ref="C93:C95"/>
     <mergeCell ref="D93:D95"/>
     <mergeCell ref="B93:B95"/>
@@ -3711,75 +3770,19 @@
     <mergeCell ref="D104:D106"/>
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="C107:C109"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="D90:D92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="D72:D75"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="A13:A67"/>
-    <mergeCell ref="D68:D71"/>
-    <mergeCell ref="C68:C71"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="D47:D51"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="D52:D56"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="D31:D36"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="D19:D24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="D25:D30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D13:D18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A3:A12"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D121:D123"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3801,14 +3804,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -3838,7 +3841,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3999,7 +4002,7 @@
   <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="16.149999999999999"/>
   <cols>
-    <col min="1" max="1" width="14" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.69921875" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.296875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.59765625" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.296875" style="12" customWidth="1"/>
@@ -4010,14 +4013,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -4043,12 +4046,14 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="8"/>
-      <c r="B3" s="20" t="s">
+      <c r="A3" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="14"/>
+      <c r="D3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -4056,36 +4061,36 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="8"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="15"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="12" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="8"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="15"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="20"/>
       <c r="E5" s="12" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="8"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="16"/>
       <c r="E6" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="8"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="12" t="s">
         <v>15</v>
       </c>
@@ -4094,7 +4099,7 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="8"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="17" t="s">
         <v>159</v>
       </c>
@@ -4107,7 +4112,7 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="8"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -4116,7 +4121,7 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="8"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="19"/>
@@ -4125,7 +4130,7 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="8"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="13" t="s">
@@ -4136,12 +4141,12 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="8"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="17" t="s">
         <v>160</v>
       </c>
       <c r="C12" s="17"/>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="12" t="s">
@@ -4149,43 +4154,43 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="8"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
-      <c r="D13" s="15"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="12" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="8"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
-      <c r="D14" s="15"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="8"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
-      <c r="D15" s="15"/>
+      <c r="D15" s="20"/>
       <c r="E15" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="8"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="15"/>
+      <c r="D16" s="20"/>
       <c r="E16" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="8"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="16"/>
@@ -4194,7 +4199,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="8"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
       <c r="D18" s="13" t="s">
@@ -4205,7 +4210,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="8"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="17" t="s">
         <v>161</v>
       </c>
@@ -4218,7 +4223,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="8"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
       <c r="D20" s="13" t="s">
@@ -4229,7 +4234,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="8"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="17" t="s">
         <v>162</v>
       </c>
@@ -4242,7 +4247,7 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="8"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="17" t="s">
@@ -4253,7 +4258,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="8"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
@@ -4262,7 +4267,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="8"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -4271,7 +4276,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="8"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="17" t="s">
         <v>163</v>
       </c>
@@ -4281,7 +4286,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="8"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="13" t="s">
@@ -4289,6 +4294,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
+      <c r="A27" s="18"/>
       <c r="B27" s="17" t="s">
         <v>164</v>
       </c>
@@ -4301,6 +4307,7 @@
       </c>
     </row>
     <row r="28" spans="1:5">
+      <c r="A28" s="18"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -4309,6 +4316,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
+      <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -4317,6 +4325,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
+      <c r="A30" s="18"/>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -4325,6 +4334,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
+      <c r="A31" s="18"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -4333,6 +4343,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
+      <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
       <c r="D32" s="19"/>
@@ -4340,7 +4351,8 @@
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="1:5">
+      <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
       <c r="D33" s="17" t="s">
@@ -4350,7 +4362,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="1:5">
+      <c r="A34" s="18"/>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -4358,59 +4371,66 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" spans="1:5">
+      <c r="A35" s="18"/>
       <c r="B35" s="17" t="s">
         <v>165</v>
       </c>
       <c r="C35" s="17"/>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="14" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="1:5">
+      <c r="A36" s="18"/>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="20"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="1:5">
+      <c r="A37" s="18"/>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="20"/>
+      <c r="D37" s="14"/>
       <c r="E37" s="12" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="1:5">
+      <c r="A38" s="18"/>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="20"/>
+      <c r="D38" s="14"/>
       <c r="E38" s="12" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
+    <row r="39" spans="1:5">
+      <c r="A39" s="18"/>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="20"/>
+      <c r="D39" s="14"/>
       <c r="E39" s="12" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="1:5">
+      <c r="A40" s="18"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="20"/>
+      <c r="D40" s="14"/>
       <c r="E40" s="12" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="1:5">
+      <c r="A41" s="18"/>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
       <c r="D41" s="18" t="s">
@@ -4420,7 +4440,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="1:5">
+      <c r="A42" s="18"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
@@ -4428,7 +4449,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="1:5">
+      <c r="A43" s="18"/>
       <c r="B43" s="17" t="s">
         <v>166</v>
       </c>
@@ -4440,7 +4462,8 @@
         <v>197</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
+    <row r="44" spans="1:5">
+      <c r="A44" s="18"/>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
@@ -4448,7 +4471,8 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
+    <row r="45" spans="1:5">
+      <c r="A45" s="18"/>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
       <c r="D45" s="18"/>
@@ -4456,7 +4480,8 @@
         <v>198</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
+    <row r="46" spans="1:5">
+      <c r="A46" s="18"/>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
       <c r="D46" s="18"/>
@@ -4464,7 +4489,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="2:5">
+    <row r="47" spans="1:5">
+      <c r="A47" s="18"/>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
       <c r="D47" s="18"/>
@@ -4472,7 +4498,8 @@
         <v>199</v>
       </c>
     </row>
-    <row r="48" spans="2:5">
+    <row r="48" spans="1:5">
+      <c r="A48" s="18"/>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
       <c r="D48" s="18"/>
@@ -4480,7 +4507,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
+    <row r="49" spans="1:5">
+      <c r="A49" s="18"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
       <c r="D49" s="19"/>
@@ -4488,7 +4516,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
+    <row r="50" spans="1:5">
+      <c r="A50" s="18"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
       <c r="D50" s="17" t="s">
@@ -4498,7 +4527,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
+    <row r="51" spans="1:5">
+      <c r="A51" s="18"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
@@ -4506,7 +4536,8 @@
         <v>194</v>
       </c>
     </row>
-    <row r="52" spans="2:5">
+    <row r="52" spans="1:5">
+      <c r="A52" s="18"/>
       <c r="B52" s="17" t="s">
         <v>167</v>
       </c>
@@ -4518,7 +4549,8 @@
         <v>201</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="1:5">
+      <c r="A53" s="18"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
       <c r="D53" s="19"/>
@@ -4526,7 +4558,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" spans="1:5">
+      <c r="A54" s="18"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
       <c r="D54" s="12" t="s">
@@ -4536,7 +4569,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="55" spans="2:5">
+    <row r="55" spans="1:5">
+      <c r="A55" s="18"/>
       <c r="B55" s="17" t="s">
         <v>168</v>
       </c>
@@ -4548,7 +4582,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="2:5">
+    <row r="56" spans="1:5">
+      <c r="A56" s="18"/>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
@@ -4556,7 +4591,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="57" spans="2:5">
+    <row r="57" spans="1:5">
+      <c r="A57" s="18"/>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
       <c r="D57" s="19"/>
@@ -4564,7 +4600,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="58" spans="2:5">
+    <row r="58" spans="1:5">
+      <c r="A58" s="19"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="12" t="s">
@@ -4575,7 +4612,33 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="D12:D17"/>
+    <mergeCell ref="C12:C18"/>
+    <mergeCell ref="B12:B18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="D35:D40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="C35:C42"/>
+    <mergeCell ref="B35:B42"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D27:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C27:C34"/>
+    <mergeCell ref="B27:B34"/>
     <mergeCell ref="D55:D57"/>
     <mergeCell ref="C55:C58"/>
     <mergeCell ref="B55:B58"/>
@@ -4586,31 +4649,6 @@
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="C52:C54"/>
     <mergeCell ref="B52:B54"/>
-    <mergeCell ref="D35:D40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C35:C42"/>
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D27:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="C27:C34"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="D12:D17"/>
-    <mergeCell ref="C12:C18"/>
-    <mergeCell ref="B12:B18"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/code_introduction.xlsx
+++ b/code_introduction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pycharm Project\2EH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1368C001-AF09-419C-BEC4-5D8FD5E85247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B2CC6C-8F7A-4617-9395-366EF98AB93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" activeTab="5" xr2:uid="{F88859C5-A072-4064-BA9E-C15A92D606DA}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="243">
   <si>
     <t>降維統計方法</t>
   </si>
@@ -604,9 +604,6 @@
   </si>
   <si>
     <t xml:space="preserve">end_time </t>
-  </si>
-  <si>
-    <t>time_low</t>
   </si>
   <si>
     <t>series</t>
@@ -699,6 +696,123 @@
   </si>
   <si>
     <t>preprocessing</t>
+  </si>
+  <si>
+    <t>拿取數據位置</t>
+  </si>
+  <si>
+    <t>結束位置</t>
+  </si>
+  <si>
+    <t>採樣好的數據</t>
+  </si>
+  <si>
+    <t>根據間隔直接採樣</t>
+  </si>
+  <si>
+    <t>擴展多少倍</t>
+  </si>
+  <si>
+    <t>時間欄位</t>
+  </si>
+  <si>
+    <t>拓展時間與數據</t>
+  </si>
+  <si>
+    <t>拓展完數據</t>
+  </si>
+  <si>
+    <t>起始時間</t>
+  </si>
+  <si>
+    <t>結束時間</t>
+  </si>
+  <si>
+    <t>採樣頻率</t>
+  </si>
+  <si>
+    <t>根據時間間隔做採樣</t>
+  </si>
+  <si>
+    <t>數據時間</t>
+  </si>
+  <si>
+    <t>數據間隔時間</t>
+  </si>
+  <si>
+    <t>計算數據間隔時間</t>
+  </si>
+  <si>
+    <t>數據標準化</t>
+  </si>
+  <si>
+    <t>標準化完的數據</t>
+  </si>
+  <si>
+    <t>平均</t>
+  </si>
+  <si>
+    <t>標準差</t>
+  </si>
+  <si>
+    <t>多個起始時間</t>
+  </si>
+  <si>
+    <t>多個結束時間</t>
+  </si>
+  <si>
+    <t>根據時間間隔做採樣
+多個時間</t>
+  </si>
+  <si>
+    <t>分段的位置</t>
+  </si>
+  <si>
+    <t>程序輸入變數</t>
+  </si>
+  <si>
+    <t>程序輸出變數</t>
+  </si>
+  <si>
+    <t>輸入變數 時序多長</t>
+  </si>
+  <si>
+    <t>輸出變數 時序多長</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moving window 移動多少 </t>
+  </si>
+  <si>
+    <t>程序輸入變數3D數據</t>
+  </si>
+  <si>
+    <t>2D數據排成3D數據
+(RNN,LSTM,GRU,S2S)</t>
+  </si>
+  <si>
+    <t>多段2D數據排成3D數據
+(RNN,LSTM,GRU,S2S)</t>
+  </si>
+  <si>
+    <t>多個程序輸入變數</t>
+  </si>
+  <si>
+    <t>多個程序輸出變數</t>
+  </si>
+  <si>
+    <t>數據錯誤的範圍</t>
+  </si>
+  <si>
+    <t>數據錯誤位置</t>
+  </si>
+  <si>
+    <t>多少當一個範圍</t>
+  </si>
+  <si>
+    <t>輸出範圍</t>
+  </si>
+  <si>
+    <t>列出nan位置</t>
   </si>
 </sst>
 </file>
@@ -793,7 +907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -840,6 +954,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -852,8 +969,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1205,14 +1322,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1239,13 +1356,13 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="15" t="s">
@@ -1259,10 +1376,10 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="16"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1271,10 +1388,10 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="17" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="18" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1285,10 +1402,10 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
@@ -1297,10 +1414,10 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1309,10 +1426,10 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
       <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1321,10 +1438,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1333,13 +1450,13 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="15" t="s">
@@ -1353,10 +1470,10 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="20"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
@@ -1365,10 +1482,10 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="20"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="16"/>
       <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1377,10 +1494,10 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
@@ -1389,10 +1506,10 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="3" t="s">
         <v>31</v>
       </c>
@@ -1401,10 +1518,10 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="20"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="3" t="s">
         <v>32</v>
       </c>
@@ -1413,10 +1530,10 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="20"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="16"/>
       <c r="E16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1425,10 +1542,10 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="20"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="3" t="s">
         <v>34</v>
       </c>
@@ -1437,10 +1554,10 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="16"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="3" t="s">
         <v>35</v>
       </c>
@@ -1449,9 +1566,9 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1463,16 +1580,16 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -1483,10 +1600,10 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
       <c r="E21" s="3" t="s">
         <v>49</v>
       </c>
@@ -1495,10 +1612,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
       <c r="E22" s="3" t="s">
         <v>50</v>
       </c>
@@ -1507,10 +1624,10 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
       <c r="E23" s="3" t="s">
         <v>9</v>
       </c>
@@ -1519,10 +1636,10 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
       <c r="E24" s="3" t="s">
         <v>33</v>
       </c>
@@ -1531,10 +1648,10 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
       <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
@@ -1543,9 +1660,9 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="3" t="s">
         <v>15</v>
       </c>
@@ -1558,6 +1675,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="A3:A9"/>
     <mergeCell ref="D10:D18"/>
     <mergeCell ref="C10:C19"/>
     <mergeCell ref="A10:A19"/>
@@ -1566,12 +1689,6 @@
     <mergeCell ref="C20:C26"/>
     <mergeCell ref="B20:B26"/>
     <mergeCell ref="A20:A26"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D9"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="A3:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1593,14 +1710,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
@@ -1736,14 +1853,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1770,13 +1887,13 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="15" t="s">
@@ -1790,10 +1907,10 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="20"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="3" t="s">
         <v>64</v>
       </c>
@@ -1802,10 +1919,10 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="20"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="3" t="s">
         <v>65</v>
       </c>
@@ -1814,10 +1931,10 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="20"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
@@ -1826,10 +1943,10 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="20"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="16"/>
       <c r="E7" s="3" t="s">
         <v>67</v>
       </c>
@@ -1838,10 +1955,10 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="20"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="16"/>
       <c r="E8" s="3" t="s">
         <v>70</v>
       </c>
@@ -1850,10 +1967,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="16"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="17"/>
       <c r="E9" s="3" t="s">
         <v>68</v>
       </c>
@@ -1862,10 +1979,10 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="17" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1876,10 +1993,10 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
       <c r="E11" s="3" t="s">
         <v>57</v>
       </c>
@@ -2005,14 +2122,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -2038,16 +2155,16 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -2058,10 +2175,10 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="21"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="3" t="s">
         <v>80</v>
       </c>
@@ -2070,10 +2187,10 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="21"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="3" t="s">
         <v>81</v>
       </c>
@@ -2082,11 +2199,11 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="18" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="15" t="s">
@@ -2100,10 +2217,10 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="16"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="17"/>
       <c r="E7" s="7" t="s">
         <v>81</v>
       </c>
@@ -2112,11 +2229,11 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="18"/>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="21" t="s">
         <v>88</v>
       </c>
       <c r="D8" s="15" t="s">
@@ -2130,10 +2247,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="18"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="20"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="16"/>
       <c r="E9" s="7" t="s">
         <v>80</v>
       </c>
@@ -2142,10 +2259,10 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="16"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="7" t="s">
         <v>81</v>
       </c>
@@ -2154,11 +2271,11 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>90</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -2172,10 +2289,10 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="19"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="16"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="17"/>
       <c r="E12" s="7" t="s">
         <v>81</v>
       </c>
@@ -2184,10 +2301,10 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="18" t="s">
         <v>93</v>
       </c>
       <c r="C13" s="15" t="s">
@@ -2204,10 +2321,10 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="3" t="s">
         <v>94</v>
       </c>
@@ -2216,10 +2333,10 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="20"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="3" t="s">
         <v>95</v>
       </c>
@@ -2228,10 +2345,10 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="20"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="16"/>
       <c r="E16" s="3" t="s">
         <v>80</v>
       </c>
@@ -2240,10 +2357,10 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="20"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="12" t="s">
         <v>81</v>
       </c>
@@ -2252,10 +2369,10 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="16"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="3" t="s">
         <v>96</v>
       </c>
@@ -2264,8 +2381,8 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="18"/>
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="19"/>
+      <c r="B19" s="18" t="s">
         <v>98</v>
       </c>
       <c r="C19" s="15" t="s">
@@ -2282,10 +2399,10 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="20"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="16"/>
       <c r="E20" s="12" t="s">
         <v>94</v>
       </c>
@@ -2294,10 +2411,10 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="20"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="16"/>
       <c r="E21" s="12" t="s">
         <v>95</v>
       </c>
@@ -2306,10 +2423,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="20"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="12" t="s">
         <v>80</v>
       </c>
@@ -2318,10 +2435,10 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="20"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="16"/>
       <c r="E23" s="12" t="s">
         <v>81</v>
       </c>
@@ -2330,10 +2447,10 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="16"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="17"/>
       <c r="E24" s="12" t="s">
         <v>96</v>
       </c>
@@ -2342,8 +2459,8 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="18"/>
-      <c r="B25" s="17" t="s">
+      <c r="A25" s="19"/>
+      <c r="B25" s="18" t="s">
         <v>99</v>
       </c>
       <c r="C25" s="15" t="s">
@@ -2360,10 +2477,10 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="20"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="16"/>
       <c r="E26" s="12" t="s">
         <v>94</v>
       </c>
@@ -2372,10 +2489,10 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="20"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="16"/>
       <c r="E27" s="12" t="s">
         <v>95</v>
       </c>
@@ -2384,10 +2501,10 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="20"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="16"/>
       <c r="E28" s="12" t="s">
         <v>80</v>
       </c>
@@ -2396,10 +2513,10 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="20"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="16"/>
       <c r="E29" s="12" t="s">
         <v>81</v>
       </c>
@@ -2408,10 +2525,10 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="16"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="17"/>
       <c r="E30" s="12" t="s">
         <v>96</v>
       </c>
@@ -2420,8 +2537,8 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="18"/>
-      <c r="B31" s="17" t="s">
+      <c r="A31" s="19"/>
+      <c r="B31" s="18" t="s">
         <v>100</v>
       </c>
       <c r="C31" s="15" t="s">
@@ -2438,10 +2555,10 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="20"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="16"/>
       <c r="E32" s="12" t="s">
         <v>94</v>
       </c>
@@ -2450,10 +2567,10 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="20"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="16"/>
       <c r="E33" s="12" t="s">
         <v>95</v>
       </c>
@@ -2462,10 +2579,10 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="20"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="16"/>
       <c r="E34" s="12" t="s">
         <v>80</v>
       </c>
@@ -2474,10 +2591,10 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="20"/>
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="16"/>
       <c r="E35" s="12" t="s">
         <v>81</v>
       </c>
@@ -2486,10 +2603,10 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="16"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="17"/>
       <c r="E36" s="12" t="s">
         <v>96</v>
       </c>
@@ -2498,8 +2615,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="16.149999999999999" customHeight="1">
-      <c r="A37" s="18"/>
-      <c r="B37" s="17" t="s">
+      <c r="A37" s="19"/>
+      <c r="B37" s="18" t="s">
         <v>101</v>
       </c>
       <c r="C37" s="15" t="s">
@@ -2516,10 +2633,10 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
       <c r="E38" s="12" t="s">
         <v>94</v>
       </c>
@@ -2528,10 +2645,10 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="12" t="s">
         <v>95</v>
       </c>
@@ -2540,10 +2657,10 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
+      <c r="A40" s="19"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="12" t="s">
         <v>81</v>
       </c>
@@ -2552,10 +2669,10 @@
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="A41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
       <c r="E41" s="12" t="s">
         <v>96</v>
       </c>
@@ -2564,8 +2681,8 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="18"/>
-      <c r="B42" s="17" t="s">
+      <c r="A42" s="19"/>
+      <c r="B42" s="18" t="s">
         <v>102</v>
       </c>
       <c r="C42" s="15" t="s">
@@ -2582,10 +2699,10 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
       <c r="E43" s="12" t="s">
         <v>94</v>
       </c>
@@ -2594,10 +2711,10 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
       <c r="E44" s="12" t="s">
         <v>95</v>
       </c>
@@ -2606,10 +2723,10 @@
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
       <c r="E45" s="12" t="s">
         <v>81</v>
       </c>
@@ -2618,10 +2735,10 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
+      <c r="A46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
       <c r="E46" s="12" t="s">
         <v>96</v>
       </c>
@@ -2630,8 +2747,8 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="18"/>
-      <c r="B47" s="17" t="s">
+      <c r="A47" s="19"/>
+      <c r="B47" s="18" t="s">
         <v>103</v>
       </c>
       <c r="C47" s="15" t="s">
@@ -2648,10 +2765,10 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
       <c r="E48" s="12" t="s">
         <v>94</v>
       </c>
@@ -2660,10 +2777,10 @@
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="18"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
+      <c r="A49" s="19"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
       <c r="E49" s="12" t="s">
         <v>95</v>
       </c>
@@ -2672,10 +2789,10 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="18"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
       <c r="E50" s="12" t="s">
         <v>81</v>
       </c>
@@ -2684,10 +2801,10 @@
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="18"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
+      <c r="A51" s="19"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
       <c r="E51" s="12" t="s">
         <v>96</v>
       </c>
@@ -2696,8 +2813,8 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="18"/>
-      <c r="B52" s="17" t="s">
+      <c r="A52" s="19"/>
+      <c r="B52" s="18" t="s">
         <v>104</v>
       </c>
       <c r="C52" s="15" t="s">
@@ -2714,10 +2831,10 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="18"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
+      <c r="A53" s="19"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
       <c r="E53" s="12" t="s">
         <v>94</v>
       </c>
@@ -2726,10 +2843,10 @@
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="18"/>
-      <c r="B54" s="18"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
+      <c r="A54" s="19"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
       <c r="E54" s="12" t="s">
         <v>95</v>
       </c>
@@ -2738,10 +2855,10 @@
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="18"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
       <c r="E55" s="12" t="s">
         <v>81</v>
       </c>
@@ -2750,10 +2867,10 @@
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="18"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
+      <c r="A56" s="19"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
       <c r="E56" s="12" t="s">
         <v>96</v>
       </c>
@@ -2762,14 +2879,14 @@
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="18"/>
-      <c r="B57" s="17" t="s">
+      <c r="A57" s="19"/>
+      <c r="B57" s="18" t="s">
         <v>105</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -2780,10 +2897,10 @@
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
+      <c r="A58" s="19"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
       <c r="E58" s="12" t="s">
         <v>95</v>
       </c>
@@ -2792,10 +2909,10 @@
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="18"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
+      <c r="A59" s="19"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
       <c r="E59" s="12" t="s">
         <v>119</v>
       </c>
@@ -2804,14 +2921,14 @@
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="18"/>
-      <c r="B60" s="17" t="s">
+      <c r="A60" s="19"/>
+      <c r="B60" s="18" t="s">
         <v>106</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E60" s="12" t="s">
@@ -2822,10 +2939,10 @@
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="18"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
+      <c r="A61" s="19"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
       <c r="E61" s="12" t="s">
         <v>95</v>
       </c>
@@ -2834,10 +2951,10 @@
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
+      <c r="A62" s="19"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
       <c r="E62" s="12" t="s">
         <v>119</v>
       </c>
@@ -2846,10 +2963,10 @@
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="18"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
       <c r="E63" s="12" t="s">
         <v>96</v>
       </c>
@@ -2858,14 +2975,14 @@
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="18"/>
-      <c r="B64" s="17" t="s">
+      <c r="A64" s="19"/>
+      <c r="B64" s="18" t="s">
         <v>107</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="12" t="s">
@@ -2876,10 +2993,10 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
+      <c r="A65" s="19"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
       <c r="E65" s="12" t="s">
         <v>95</v>
       </c>
@@ -2888,10 +3005,10 @@
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
+      <c r="A66" s="19"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
       <c r="E66" s="12" t="s">
         <v>119</v>
       </c>
@@ -2900,10 +3017,10 @@
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="19"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
+      <c r="A67" s="20"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
       <c r="E67" s="12" t="s">
         <v>96</v>
       </c>
@@ -2912,16 +3029,16 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="18" t="s">
         <v>124</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -2932,10 +3049,10 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="18"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
+      <c r="A69" s="19"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
       <c r="E69" s="3" t="s">
         <v>80</v>
       </c>
@@ -2944,10 +3061,10 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="18"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
+      <c r="A70" s="19"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
       <c r="E70" s="3" t="s">
         <v>81</v>
       </c>
@@ -2956,10 +3073,10 @@
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="18"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
+      <c r="A71" s="19"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
       <c r="E71" s="3" t="s">
         <v>96</v>
       </c>
@@ -2968,14 +3085,14 @@
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="18"/>
-      <c r="B72" s="17" t="s">
+      <c r="A72" s="19"/>
+      <c r="B72" s="18" t="s">
         <v>125</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E72" s="12" t="s">
@@ -2986,10 +3103,10 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="18"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
+      <c r="A73" s="19"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
       <c r="E73" s="12" t="s">
         <v>80</v>
       </c>
@@ -2998,10 +3115,10 @@
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="18"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
+      <c r="A74" s="19"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
       <c r="E74" s="12" t="s">
         <v>81</v>
       </c>
@@ -3010,10 +3127,10 @@
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="18"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
+      <c r="A75" s="19"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
       <c r="E75" s="12" t="s">
         <v>96</v>
       </c>
@@ -3022,14 +3139,14 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="16.149999999999999" customHeight="1">
-      <c r="A76" s="18"/>
-      <c r="B76" s="17" t="s">
+      <c r="A76" s="19"/>
+      <c r="B76" s="18" t="s">
         <v>126</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E76" s="12" t="s">
@@ -3040,10 +3157,10 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="18"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="18"/>
+      <c r="A77" s="19"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="19"/>
       <c r="E77" s="12" t="s">
         <v>81</v>
       </c>
@@ -3052,10 +3169,10 @@
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="18"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="19"/>
+      <c r="A78" s="19"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="20"/>
       <c r="E78" s="12" t="s">
         <v>96</v>
       </c>
@@ -3064,14 +3181,14 @@
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="18"/>
-      <c r="B79" s="17" t="s">
+      <c r="A79" s="19"/>
+      <c r="B79" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C79" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E79" s="12" t="s">
@@ -3082,10 +3199,10 @@
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="18"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="18"/>
+      <c r="A80" s="19"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="19"/>
       <c r="E80" s="12" t="s">
         <v>81</v>
       </c>
@@ -3094,10 +3211,10 @@
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="18"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="19"/>
+      <c r="A81" s="19"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="20"/>
       <c r="E81" s="12" t="s">
         <v>96</v>
       </c>
@@ -3106,14 +3223,14 @@
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="18"/>
-      <c r="B82" s="17" t="s">
+      <c r="A82" s="19"/>
+      <c r="B82" s="18" t="s">
         <v>128</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E82" s="12" t="s">
@@ -3124,10 +3241,10 @@
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="18"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
+      <c r="A83" s="19"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
       <c r="E83" s="12" t="s">
         <v>80</v>
       </c>
@@ -3136,10 +3253,10 @@
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="18"/>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="18"/>
+      <c r="A84" s="19"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="19"/>
       <c r="E84" s="12" t="s">
         <v>81</v>
       </c>
@@ -3148,10 +3265,10 @@
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="18"/>
-      <c r="B85" s="19"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="19"/>
+      <c r="A85" s="19"/>
+      <c r="B85" s="20"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
       <c r="E85" s="12" t="s">
         <v>96</v>
       </c>
@@ -3160,14 +3277,14 @@
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="18"/>
-      <c r="B86" s="17" t="s">
+      <c r="A86" s="19"/>
+      <c r="B86" s="18" t="s">
         <v>129</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E86" s="12" t="s">
@@ -3178,10 +3295,10 @@
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="18"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
+      <c r="A87" s="19"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="19"/>
       <c r="E87" s="12" t="s">
         <v>80</v>
       </c>
@@ -3190,10 +3307,10 @@
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="18"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
+      <c r="A88" s="19"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="19"/>
       <c r="E88" s="12" t="s">
         <v>81</v>
       </c>
@@ -3202,10 +3319,10 @@
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="18"/>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
+      <c r="A89" s="19"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
       <c r="E89" s="12" t="s">
         <v>96</v>
       </c>
@@ -3214,14 +3331,14 @@
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="18"/>
-      <c r="B90" s="17" t="s">
+      <c r="A90" s="19"/>
+      <c r="B90" s="18" t="s">
         <v>130</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="D90" s="17" t="s">
+      <c r="D90" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E90" s="12" t="s">
@@ -3232,10 +3349,10 @@
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="18"/>
-      <c r="B91" s="18"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="18"/>
+      <c r="A91" s="19"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="19"/>
       <c r="E91" s="12" t="s">
         <v>81</v>
       </c>
@@ -3244,10 +3361,10 @@
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="18"/>
-      <c r="B92" s="19"/>
-      <c r="C92" s="20"/>
-      <c r="D92" s="19"/>
+      <c r="A92" s="19"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="20"/>
       <c r="E92" s="12" t="s">
         <v>96</v>
       </c>
@@ -3256,14 +3373,14 @@
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="18"/>
-      <c r="B93" s="17" t="s">
+      <c r="A93" s="19"/>
+      <c r="B93" s="18" t="s">
         <v>131</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D93" s="17" t="s">
+      <c r="D93" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E93" s="12" t="s">
@@ -3274,10 +3391,10 @@
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="18"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="20"/>
-      <c r="D94" s="18"/>
+      <c r="A94" s="19"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="19"/>
       <c r="E94" s="12" t="s">
         <v>81</v>
       </c>
@@ -3286,10 +3403,10 @@
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="19"/>
-      <c r="B95" s="19"/>
-      <c r="C95" s="20"/>
-      <c r="D95" s="19"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="20"/>
       <c r="E95" s="12" t="s">
         <v>96</v>
       </c>
@@ -3298,16 +3415,16 @@
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="17" t="s">
+      <c r="A96" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B96" s="18" t="s">
         <v>141</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="D96" s="17" t="s">
+      <c r="D96" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E96" s="12" t="s">
@@ -3318,10 +3435,10 @@
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="18"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
+      <c r="A97" s="19"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
       <c r="E97" s="12" t="s">
         <v>80</v>
       </c>
@@ -3330,10 +3447,10 @@
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="18"/>
-      <c r="B98" s="18"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
+      <c r="A98" s="19"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="19"/>
       <c r="E98" s="12" t="s">
         <v>81</v>
       </c>
@@ -3342,10 +3459,10 @@
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="18"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
+      <c r="A99" s="19"/>
+      <c r="B99" s="20"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="20"/>
       <c r="E99" s="12" t="s">
         <v>96</v>
       </c>
@@ -3354,14 +3471,14 @@
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="18"/>
-      <c r="B100" s="17" t="s">
+      <c r="A100" s="19"/>
+      <c r="B100" s="18" t="s">
         <v>142</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E100" s="12" t="s">
@@ -3372,10 +3489,10 @@
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="18"/>
-      <c r="B101" s="18"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="18"/>
+      <c r="A101" s="19"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="19"/>
+      <c r="D101" s="19"/>
       <c r="E101" s="12" t="s">
         <v>80</v>
       </c>
@@ -3384,10 +3501,10 @@
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="18"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
+      <c r="A102" s="19"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="19"/>
       <c r="E102" s="12" t="s">
         <v>81</v>
       </c>
@@ -3396,10 +3513,10 @@
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="18"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="19"/>
+      <c r="A103" s="19"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
       <c r="E103" s="12" t="s">
         <v>96</v>
       </c>
@@ -3408,14 +3525,14 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="18"/>
-      <c r="B104" s="17" t="s">
+      <c r="A104" s="19"/>
+      <c r="B104" s="18" t="s">
         <v>143</v>
       </c>
       <c r="C104" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D104" s="17" t="s">
+      <c r="D104" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E104" s="12" t="s">
@@ -3426,10 +3543,10 @@
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="18"/>
-      <c r="B105" s="18"/>
-      <c r="C105" s="20"/>
-      <c r="D105" s="18"/>
+      <c r="A105" s="19"/>
+      <c r="B105" s="19"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="19"/>
       <c r="E105" s="12" t="s">
         <v>81</v>
       </c>
@@ -3438,10 +3555,10 @@
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="18"/>
-      <c r="B106" s="19"/>
-      <c r="C106" s="20"/>
-      <c r="D106" s="19"/>
+      <c r="A106" s="19"/>
+      <c r="B106" s="20"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="20"/>
       <c r="E106" s="12" t="s">
         <v>96</v>
       </c>
@@ -3450,14 +3567,14 @@
       </c>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="18"/>
-      <c r="B107" s="17" t="s">
+      <c r="A107" s="19"/>
+      <c r="B107" s="18" t="s">
         <v>144</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D107" s="17" t="s">
+      <c r="D107" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E107" s="12" t="s">
@@ -3468,10 +3585,10 @@
       </c>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="18"/>
-      <c r="B108" s="18"/>
-      <c r="C108" s="20"/>
-      <c r="D108" s="18"/>
+      <c r="A108" s="19"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="19"/>
       <c r="E108" s="12" t="s">
         <v>81</v>
       </c>
@@ -3480,10 +3597,10 @@
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="18"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="20"/>
-      <c r="D109" s="19"/>
+      <c r="A109" s="19"/>
+      <c r="B109" s="20"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="20"/>
       <c r="E109" s="12" t="s">
         <v>96</v>
       </c>
@@ -3492,14 +3609,14 @@
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="18"/>
-      <c r="B110" s="17" t="s">
+      <c r="A110" s="19"/>
+      <c r="B110" s="18" t="s">
         <v>145</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="D110" s="17" t="s">
+      <c r="D110" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E110" s="12" t="s">
@@ -3510,10 +3627,10 @@
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="18"/>
-      <c r="B111" s="18"/>
-      <c r="C111" s="18"/>
-      <c r="D111" s="18"/>
+      <c r="A111" s="19"/>
+      <c r="B111" s="19"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="19"/>
       <c r="E111" s="12" t="s">
         <v>80</v>
       </c>
@@ -3522,10 +3639,10 @@
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="18"/>
-      <c r="B112" s="18"/>
-      <c r="C112" s="18"/>
-      <c r="D112" s="18"/>
+      <c r="A112" s="19"/>
+      <c r="B112" s="19"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="19"/>
       <c r="E112" s="12" t="s">
         <v>81</v>
       </c>
@@ -3534,10 +3651,10 @@
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="18"/>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
-      <c r="D113" s="19"/>
+      <c r="A113" s="19"/>
+      <c r="B113" s="20"/>
+      <c r="C113" s="20"/>
+      <c r="D113" s="20"/>
       <c r="E113" s="12" t="s">
         <v>96</v>
       </c>
@@ -3546,14 +3663,14 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="18"/>
-      <c r="B114" s="17" t="s">
+      <c r="A114" s="19"/>
+      <c r="B114" s="18" t="s">
         <v>146</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D114" s="17" t="s">
+      <c r="D114" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E114" s="12" t="s">
@@ -3564,10 +3681,10 @@
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="18"/>
-      <c r="B115" s="18"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
+      <c r="A115" s="19"/>
+      <c r="B115" s="19"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="19"/>
       <c r="E115" s="12" t="s">
         <v>80</v>
       </c>
@@ -3576,10 +3693,10 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="18"/>
-      <c r="B116" s="18"/>
-      <c r="C116" s="18"/>
-      <c r="D116" s="18"/>
+      <c r="A116" s="19"/>
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="19"/>
       <c r="E116" s="12" t="s">
         <v>81</v>
       </c>
@@ -3588,10 +3705,10 @@
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="18"/>
-      <c r="B117" s="19"/>
-      <c r="C117" s="19"/>
-      <c r="D117" s="19"/>
+      <c r="A117" s="19"/>
+      <c r="B117" s="20"/>
+      <c r="C117" s="20"/>
+      <c r="D117" s="20"/>
       <c r="E117" s="12" t="s">
         <v>96</v>
       </c>
@@ -3600,14 +3717,14 @@
       </c>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="18"/>
-      <c r="B118" s="17" t="s">
+      <c r="A118" s="19"/>
+      <c r="B118" s="18" t="s">
         <v>147</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D118" s="17" t="s">
+      <c r="D118" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E118" s="12" t="s">
@@ -3618,10 +3735,10 @@
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="18"/>
-      <c r="B119" s="18"/>
-      <c r="C119" s="20"/>
-      <c r="D119" s="18"/>
+      <c r="A119" s="19"/>
+      <c r="B119" s="19"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="19"/>
       <c r="E119" s="12" t="s">
         <v>81</v>
       </c>
@@ -3630,10 +3747,10 @@
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="18"/>
-      <c r="B120" s="19"/>
-      <c r="C120" s="20"/>
-      <c r="D120" s="19"/>
+      <c r="A120" s="19"/>
+      <c r="B120" s="20"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="20"/>
       <c r="E120" s="12" t="s">
         <v>96</v>
       </c>
@@ -3642,14 +3759,14 @@
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="18"/>
-      <c r="B121" s="17" t="s">
+      <c r="A121" s="19"/>
+      <c r="B121" s="18" t="s">
         <v>148</v>
       </c>
       <c r="C121" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="D121" s="17" t="s">
+      <c r="D121" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E121" s="12" t="s">
@@ -3660,10 +3777,10 @@
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="18"/>
-      <c r="B122" s="18"/>
-      <c r="C122" s="20"/>
-      <c r="D122" s="18"/>
+      <c r="A122" s="19"/>
+      <c r="B122" s="19"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="19"/>
       <c r="E122" s="12" t="s">
         <v>81</v>
       </c>
@@ -3672,10 +3789,10 @@
       </c>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="19"/>
-      <c r="B123" s="19"/>
-      <c r="C123" s="20"/>
-      <c r="D123" s="19"/>
+      <c r="A123" s="20"/>
+      <c r="B123" s="20"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="20"/>
       <c r="E123" s="12" t="s">
         <v>96</v>
       </c>
@@ -3685,6 +3802,88 @@
     </row>
   </sheetData>
   <mergeCells count="98">
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D121:D123"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="A68:A95"/>
+    <mergeCell ref="A96:A123"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="D104:D106"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="D90:D92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="D79:D81"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="A13:A67"/>
+    <mergeCell ref="D68:D71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="D47:D51"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="D52:D56"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="D31:D36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="D19:D24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="D25:D30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B25:B30"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B3:B5"/>
@@ -3701,88 +3900,6 @@
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="D31:D36"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="D19:D24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="D25:D30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="D52:D56"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="A13:A67"/>
-    <mergeCell ref="D68:D71"/>
-    <mergeCell ref="C68:C71"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="D47:D51"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="D72:D75"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="D90:D92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="A68:A95"/>
-    <mergeCell ref="A96:A123"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="C96:C99"/>
-    <mergeCell ref="D96:D99"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="C100:C103"/>
-    <mergeCell ref="D100:D103"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="D121:D123"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3804,14 +3921,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -3838,50 +3955,50 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
       <c r="D3" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="16"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="17"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="17" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="8"/>
@@ -3999,7 +4116,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89F3D3C-6CDD-4026-851E-F3F25E51AE26}">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr defaultRowHeight="16.149999999999999"/>
   <cols>
     <col min="1" max="1" width="15.69921875" style="3" customWidth="1"/>
@@ -4013,14 +4130,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -4046,609 +4163,767 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="14"/>
+      <c r="C3" s="21" t="s">
+        <v>208</v>
+      </c>
       <c r="D3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="20"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="12" t="s">
         <v>169</v>
       </c>
+      <c r="F4" s="3" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="20"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="12" t="s">
         <v>170</v>
       </c>
+      <c r="F5" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="16"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="12" t="s">
         <v>171</v>
       </c>
+      <c r="F6" s="3" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="12" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>172</v>
       </c>
+      <c r="F7" s="3" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="18"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17" t="s">
+      <c r="C8" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="F8" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
       <c r="E9" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="F9" s="3" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="12" t="s">
         <v>174</v>
       </c>
+      <c r="F10" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="13" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>175</v>
       </c>
+      <c r="F11" s="3" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="18"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="17"/>
+      <c r="C12" s="18" t="s">
+        <v>216</v>
+      </c>
       <c r="D12" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>8</v>
       </c>
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="12" t="s">
         <v>176</v>
       </c>
+      <c r="F13" s="3" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="12" t="s">
         <v>177</v>
       </c>
+      <c r="F14" s="3" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="20"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="12" t="s">
         <v>171</v>
       </c>
+      <c r="F15" s="3" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="20"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="16"/>
       <c r="E16" s="12" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="16"/>
+      <c r="F16" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="E17" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="19"/>
+      <c r="B18" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="13" t="s">
+      <c r="F18" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="13" t="s">
         <v>15</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="18"/>
-      <c r="B19" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="12" t="s">
-        <v>14</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="13" t="s">
+      <c r="F19" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="19"/>
+      <c r="B20" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E21" s="12" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="18"/>
-      <c r="B21" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="17" t="s">
-        <v>15</v>
-      </c>
+      <c r="F21" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
       <c r="E22" s="12" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="F22" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
       <c r="E23" s="12" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="12" t="s">
+      <c r="F23" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="19"/>
+      <c r="B24" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="12" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="18"/>
-      <c r="B25" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="18"/>
-      <c r="B27" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
+      <c r="F27" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
       <c r="E28" s="12" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
+      <c r="F28" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
       <c r="E29" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="12" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17" t="s">
-        <v>15</v>
+      <c r="F32" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="19"/>
+      <c r="B33" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="18"/>
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="19"/>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
+      <c r="D34" s="21"/>
       <c r="E34" s="12" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="18"/>
-      <c r="B35" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="14" t="s">
-        <v>14</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="21"/>
       <c r="E35" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="14"/>
+        <v>187</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="21"/>
       <c r="E36" s="12" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="14"/>
+      <c r="F36" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="12" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="14"/>
+        <v>190</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="21"/>
       <c r="E38" s="12" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="14"/>
+        <v>191</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19" t="s">
+        <v>15</v>
+      </c>
       <c r="E39" s="12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="14"/>
+        <v>194</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
       <c r="E40" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
+        <v>195</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="19"/>
+      <c r="B41" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>235</v>
+      </c>
       <c r="D41" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="18"/>
+        <v>196</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="19"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
       <c r="E42" s="12" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="18"/>
-      <c r="B43" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17" t="s">
-        <v>14</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
       <c r="E43" s="12" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
+      <c r="F43" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="19"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
       <c r="E44" s="12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
+        <v>189</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
       <c r="E45" s="12" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
+      <c r="F45" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
       <c r="E46" s="12" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
+        <v>199</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
       <c r="E47" s="12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
+        <v>185</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="18" t="s">
+        <v>15</v>
+      </c>
       <c r="E48" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="19"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="19"/>
+      <c r="B50" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="18"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="12" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="18"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="18"/>
+      <c r="F50" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="19"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
+      <c r="D51" s="20"/>
       <c r="E51" s="12" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="18"/>
-      <c r="B52" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="19"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="19"/>
+      <c r="B53" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D53" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E52" s="12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="18"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="19"/>
       <c r="E53" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="18"/>
+        <v>8</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="19"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
-      <c r="D54" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="D54" s="19"/>
       <c r="E54" s="12" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="18"/>
-      <c r="B55" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17" t="s">
-        <v>14</v>
-      </c>
+      <c r="F54" s="14" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="20"/>
       <c r="E55" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="18"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="18"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>8</v>
+      <c r="F56" s="14" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="D41:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="C41:C49"/>
+    <mergeCell ref="B41:B49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="D33:D38"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="C33:C40"/>
+    <mergeCell ref="B33:B40"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C26:C32"/>
+    <mergeCell ref="B26:B32"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="A3:A56"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="B8:B11"/>
-    <mergeCell ref="D12:D17"/>
-    <mergeCell ref="C12:C18"/>
-    <mergeCell ref="B12:B18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="D35:D40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="C35:C42"/>
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D27:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="C27:C34"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="C55:C58"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="D43:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="C43:C51"/>
-    <mergeCell ref="B43:B51"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="C12:C17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="B20:B23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/code_introduction.xlsx
+++ b/code_introduction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pycharm Project\2EH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B2CC6C-8F7A-4617-9395-366EF98AB93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F99D4B8-B0CF-44E1-AD28-788A5E4C2BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" activeTab="5" xr2:uid="{F88859C5-A072-4064-BA9E-C15A92D606DA}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" activeTab="3" xr2:uid="{F88859C5-A072-4064-BA9E-C15A92D606DA}"/>
   </bookViews>
   <sheets>
     <sheet name="dim_reduce" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="263">
   <si>
     <t>降維統計方法</t>
   </si>
@@ -813,6 +813,67 @@
   </si>
   <si>
     <t>列出nan位置</t>
+  </si>
+  <si>
+    <t>k_fold</t>
+  </si>
+  <si>
+    <t>all_length</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>equal_division</t>
+  </si>
+  <si>
+    <t>train_idx</t>
+  </si>
+  <si>
+    <t>test_idx</t>
+  </si>
+  <si>
+    <t>分割出k-fold第i等分的
+訓練集與測試集</t>
+  </si>
+  <si>
+    <t>第幾等分</t>
+  </si>
+  <si>
+    <t>分幾等分</t>
+  </si>
+  <si>
+    <t>訓練集</t>
+  </si>
+  <si>
+    <t>測試集</t>
+  </si>
+  <si>
+    <t>全部數據長度</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>xlabel</t>
+  </si>
+  <si>
+    <t>ylabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">figure_name </t>
+  </si>
+  <si>
+    <t>圖的title</t>
+  </si>
+  <si>
+    <t>圖的xlabel</t>
+  </si>
+  <si>
+    <t>圖的ylabel</t>
+  </si>
+  <si>
+    <t>檔名</t>
   </si>
 </sst>
 </file>
@@ -907,7 +968,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -951,10 +1012,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -969,8 +1033,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1322,14 +1386,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1356,16 +1420,16 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1376,10 +1440,10 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="17"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1388,10 +1452,10 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="18" t="s">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="19" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1402,10 +1466,10 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
@@ -1414,10 +1478,10 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1426,10 +1490,10 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1438,10 +1502,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1450,16 +1514,16 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1470,10 +1534,10 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="16"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="22"/>
       <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
@@ -1482,10 +1546,10 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="16"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="22"/>
       <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1494,10 +1558,10 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="16"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
       <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
@@ -1506,10 +1570,10 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="16"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="3" t="s">
         <v>31</v>
       </c>
@@ -1518,10 +1582,10 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="16"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="22"/>
       <c r="E15" s="3" t="s">
         <v>32</v>
       </c>
@@ -1530,10 +1594,10 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="16"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1542,10 +1606,10 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="16"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="22"/>
       <c r="E17" s="3" t="s">
         <v>34</v>
       </c>
@@ -1554,10 +1618,10 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="17"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="18"/>
       <c r="E18" s="3" t="s">
         <v>35</v>
       </c>
@@ -1566,9 +1630,9 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1580,16 +1644,16 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -1600,10 +1664,10 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
       <c r="E21" s="3" t="s">
         <v>49</v>
       </c>
@@ -1612,10 +1676,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
       <c r="E22" s="3" t="s">
         <v>50</v>
       </c>
@@ -1624,10 +1688,10 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
       <c r="E23" s="3" t="s">
         <v>9</v>
       </c>
@@ -1636,10 +1700,10 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
       <c r="E24" s="3" t="s">
         <v>33</v>
       </c>
@@ -1648,10 +1712,10 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="3" t="s">
         <v>34</v>
       </c>
@@ -1660,9 +1724,9 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="3" t="s">
         <v>15</v>
       </c>
@@ -1675,12 +1739,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D9"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="A3:A9"/>
     <mergeCell ref="D10:D18"/>
     <mergeCell ref="C10:C19"/>
     <mergeCell ref="A10:A19"/>
@@ -1689,6 +1747,12 @@
     <mergeCell ref="C20:C26"/>
     <mergeCell ref="B20:B26"/>
     <mergeCell ref="A20:A26"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="A3:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1710,14 +1774,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
@@ -1853,14 +1917,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1887,16 +1951,16 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1907,10 +1971,10 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="16"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="3" t="s">
         <v>64</v>
       </c>
@@ -1919,10 +1983,10 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="16"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="3" t="s">
         <v>65</v>
       </c>
@@ -1931,10 +1995,10 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="16"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
@@ -1943,10 +2007,10 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="16"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="22"/>
       <c r="E7" s="3" t="s">
         <v>67</v>
       </c>
@@ -1955,10 +2019,10 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="16"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="22"/>
       <c r="E8" s="3" t="s">
         <v>70</v>
       </c>
@@ -1967,10 +2031,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="3" t="s">
         <v>68</v>
       </c>
@@ -1979,10 +2043,10 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="19" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1993,10 +2057,10 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="3" t="s">
         <v>57</v>
       </c>
@@ -2108,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1864DFD3-8A4E-4D94-AFAC-AC3B4B5A915B}">
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr defaultRowHeight="16.149999999999999"/>
   <cols>
     <col min="1" max="1" width="14" style="3" customWidth="1"/>
@@ -2122,14 +2186,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -2155,16 +2219,16 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="23" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -2175,10 +2239,10 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="19"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="3" t="s">
         <v>80</v>
       </c>
@@ -2187,708 +2251,706 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="19"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="22"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>110</v>
       </c>
+      <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="19"/>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="20"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="20"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="20"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="G8" s="15"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="20"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="20"/>
+      <c r="B10" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="7" t="s">
+    <row r="11" spans="1:10">
+      <c r="A11" s="20"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="19"/>
-      <c r="B8" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="19"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="19"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="17"/>
+      <c r="B12" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>14</v>
+      </c>
       <c r="E12" s="7" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="20"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="20"/>
+      <c r="B15" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="21"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B17" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C17" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="19"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="17"/>
+      <c r="D18" s="22"/>
       <c r="E18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="19"/>
-      <c r="B19" s="18" t="s">
+    <row r="23" spans="1:6">
+      <c r="A23" s="20"/>
+      <c r="B23" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C23" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D23" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E23" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F23" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="19"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
-      <c r="D24" s="17"/>
+      <c r="D24" s="22"/>
       <c r="E24" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="20"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F28" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="19"/>
-      <c r="B25" s="18" t="s">
+    <row r="29" spans="1:6">
+      <c r="A29" s="20"/>
+      <c r="B29" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C29" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D29" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E29" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F29" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="19"/>
+      <c r="A30" s="20"/>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
-      <c r="D30" s="17"/>
+      <c r="D30" s="22"/>
       <c r="E30" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="20"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F34" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="19"/>
-      <c r="B31" s="18" t="s">
+    <row r="35" spans="1:6">
+      <c r="A35" s="20"/>
+      <c r="B35" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C35" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D35" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E35" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F35" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="19"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
-      <c r="D36" s="17"/>
+      <c r="D36" s="22"/>
       <c r="E36" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F40" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="16.149999999999999" customHeight="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="18" t="s">
+    <row r="41" spans="1:6" ht="16.149999999999999" customHeight="1">
+      <c r="A41" s="20"/>
+      <c r="B41" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C41" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D41" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E41" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F41" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="12" t="s">
+    <row r="42" spans="1:6">
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F42" s="12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="12" t="s">
+    <row r="43" spans="1:6">
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F43" s="12" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="19"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="12" t="s">
+    <row r="44" spans="1:6">
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F44" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="19"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="12" t="s">
+    <row r="45" spans="1:6">
+      <c r="A45" s="20"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F45" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="19"/>
-      <c r="B42" s="18" t="s">
+    <row r="46" spans="1:6">
+      <c r="A46" s="20"/>
+      <c r="B46" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C46" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D46" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E46" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F46" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="12" t="s">
+    <row r="47" spans="1:6">
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F47" s="12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="12" t="s">
+    <row r="48" spans="1:6">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F48" s="12" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="12" t="s">
+    <row r="49" spans="1:6">
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F49" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="19"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="12" t="s">
+    <row r="50" spans="1:6">
+      <c r="A50" s="20"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F50" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="19"/>
-      <c r="B47" s="18" t="s">
+    <row r="51" spans="1:6">
+      <c r="A51" s="20"/>
+      <c r="B51" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C51" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D51" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E51" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F51" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="12" t="s">
+    <row r="52" spans="1:6">
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F52" s="12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="12" t="s">
+    <row r="53" spans="1:6">
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F53" s="12" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="19"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="12" t="s">
+    <row r="54" spans="1:6">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F54" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="19"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="12" t="s">
+    <row r="55" spans="1:6">
+      <c r="A55" s="20"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F55" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="19"/>
-      <c r="B52" s="18" t="s">
+    <row r="56" spans="1:6">
+      <c r="A56" s="20"/>
+      <c r="B56" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C56" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D56" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E56" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F56" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="19"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="19"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="19"/>
-      <c r="B57" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>14</v>
-      </c>
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
       <c r="E57" s="12" t="s">
         <v>94</v>
       </c>
@@ -2897,10 +2959,10 @@
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
       <c r="E58" s="12" t="s">
         <v>95</v>
       </c>
@@ -2909,80 +2971,80 @@
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="19"/>
+      <c r="A59" s="20"/>
       <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
       <c r="E59" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="20"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="20"/>
+      <c r="B61" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="20"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="19"/>
-      <c r="B60" s="18" t="s">
+    <row r="64" spans="1:6">
+      <c r="A64" s="20"/>
+      <c r="B64" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C64" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D60" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="19"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="19"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="19"/>
-      <c r="B64" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="12" t="s">
@@ -2993,10 +3055,10 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="19"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
+      <c r="A65" s="20"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
       <c r="E65" s="12" t="s">
         <v>95</v>
       </c>
@@ -3005,10 +3067,10 @@
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="19"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
+      <c r="A66" s="20"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
       <c r="E66" s="12" t="s">
         <v>119</v>
       </c>
@@ -3018,9 +3080,9 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="20"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
       <c r="E67" s="12" t="s">
         <v>96</v>
       </c>
@@ -3029,55 +3091,53 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D68" s="18" t="s">
+      <c r="A68" s="20"/>
+      <c r="B68" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D68" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>8</v>
+      <c r="E68" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="19"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>91</v>
+      <c r="A69" s="20"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="19"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="3" t="s">
-        <v>81</v>
+      <c r="A70" s="20"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="19"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="3" t="s">
+      <c r="A71" s="21"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="12" t="s">
         <v>96</v>
       </c>
       <c r="F71" s="12" t="s">
@@ -3085,17 +3145,19 @@
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="19"/>
-      <c r="B72" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D72" s="18" t="s">
+      <c r="A72" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="12" t="s">
@@ -3103,23 +3165,23 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="19"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="12" t="s">
+      <c r="A73" s="20"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F73" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="19"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="12" t="s">
+      <c r="A74" s="20"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F74" s="12" t="s">
@@ -3127,26 +3189,26 @@
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="19"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="12" t="s">
+      <c r="A75" s="20"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="16.149999999999999" customHeight="1">
-      <c r="A76" s="19"/>
-      <c r="B76" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D76" s="18" t="s">
+    <row r="76" spans="1:6">
+      <c r="A76" s="20"/>
+      <c r="B76" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D76" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E76" s="12" t="s">
@@ -3157,106 +3219,106 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="19"/>
-      <c r="B77" s="19"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="19"/>
+      <c r="A77" s="20"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
       <c r="E77" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="19"/>
+      <c r="A78" s="20"/>
       <c r="B78" s="20"/>
-      <c r="C78" s="16"/>
+      <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="20"/>
+      <c r="B79" s="21"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F78" s="12" t="s">
+      <c r="F79" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="19"/>
-      <c r="B79" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D79" s="18" t="s">
+    <row r="80" spans="1:6" ht="16.149999999999999" customHeight="1">
+      <c r="A80" s="20"/>
+      <c r="B80" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D80" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E80" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F79" s="12" t="s">
+      <c r="F80" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="19"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="19"/>
+      <c r="A81" s="20"/>
       <c r="B81" s="20"/>
-      <c r="C81" s="16"/>
+      <c r="C81" s="22"/>
       <c r="D81" s="20"/>
       <c r="E81" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="20"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="22"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="F82" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="19"/>
-      <c r="B82" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C82" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D82" s="18" t="s">
+    <row r="83" spans="1:6">
+      <c r="A83" s="20"/>
+      <c r="B83" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D83" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E82" s="12" t="s">
+      <c r="E83" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="F83" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83" s="19"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F83" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="19"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="20"/>
       <c r="E84" s="12" t="s">
         <v>81</v>
       </c>
@@ -3265,10 +3327,10 @@
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="19"/>
-      <c r="B85" s="20"/>
-      <c r="C85" s="20"/>
-      <c r="D85" s="20"/>
+      <c r="A85" s="20"/>
+      <c r="B85" s="21"/>
+      <c r="C85" s="22"/>
+      <c r="D85" s="21"/>
       <c r="E85" s="12" t="s">
         <v>96</v>
       </c>
@@ -3277,14 +3339,14 @@
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="19"/>
-      <c r="B86" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D86" s="18" t="s">
+      <c r="A86" s="20"/>
+      <c r="B86" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D86" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E86" s="12" t="s">
@@ -3295,10 +3357,10 @@
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="19"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
+      <c r="A87" s="20"/>
+      <c r="B87" s="20"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
       <c r="E87" s="12" t="s">
         <v>80</v>
       </c>
@@ -3307,10 +3369,10 @@
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="19"/>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="19"/>
+      <c r="A88" s="20"/>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
       <c r="E88" s="12" t="s">
         <v>81</v>
       </c>
@@ -3319,10 +3381,10 @@
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="19"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="20"/>
-      <c r="D89" s="20"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
       <c r="E89" s="12" t="s">
         <v>96</v>
       </c>
@@ -3331,14 +3393,14 @@
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="19"/>
-      <c r="B90" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D90" s="18" t="s">
+      <c r="A90" s="20"/>
+      <c r="B90" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E90" s="12" t="s">
@@ -3349,108 +3411,106 @@
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="19"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="19"/>
+      <c r="A91" s="20"/>
+      <c r="B91" s="20"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="20"/>
       <c r="E91" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="19"/>
+      <c r="A92" s="20"/>
       <c r="B92" s="20"/>
-      <c r="C92" s="16"/>
+      <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="20"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F92" s="12" t="s">
+      <c r="F93" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="A93" s="19"/>
-      <c r="B93" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D93" s="18" t="s">
+    <row r="94" spans="1:6">
+      <c r="A94" s="20"/>
+      <c r="B94" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D94" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E93" s="12" t="s">
+      <c r="E94" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F93" s="12" t="s">
+      <c r="F94" s="12" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" s="19"/>
-      <c r="B94" s="19"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="20"/>
       <c r="B95" s="20"/>
-      <c r="C95" s="16"/>
+      <c r="C95" s="22"/>
       <c r="D95" s="20"/>
       <c r="E95" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="20"/>
+      <c r="B96" s="21"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F95" s="12" t="s">
+      <c r="F96" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B96" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D96" s="18" t="s">
+    <row r="97" spans="1:6">
+      <c r="A97" s="20"/>
+      <c r="B97" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D97" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="E97" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="12" t="s">
+      <c r="F97" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="A97" s="19"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F97" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="19"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
+      <c r="A98" s="20"/>
+      <c r="B98" s="20"/>
+      <c r="C98" s="22"/>
+      <c r="D98" s="20"/>
       <c r="E98" s="12" t="s">
         <v>81</v>
       </c>
@@ -3459,10 +3519,10 @@
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="19"/>
-      <c r="B99" s="20"/>
-      <c r="C99" s="20"/>
-      <c r="D99" s="20"/>
+      <c r="A99" s="21"/>
+      <c r="B99" s="21"/>
+      <c r="C99" s="22"/>
+      <c r="D99" s="21"/>
       <c r="E99" s="12" t="s">
         <v>96</v>
       </c>
@@ -3471,14 +3531,16 @@
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="19"/>
-      <c r="B100" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D100" s="18" t="s">
+      <c r="A100" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="D100" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E100" s="12" t="s">
@@ -3489,10 +3551,10 @@
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="19"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
+      <c r="A101" s="20"/>
+      <c r="B101" s="20"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="20"/>
       <c r="E101" s="12" t="s">
         <v>80</v>
       </c>
@@ -3501,10 +3563,10 @@
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="19"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-      <c r="D102" s="19"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="20"/>
       <c r="E102" s="12" t="s">
         <v>81</v>
       </c>
@@ -3513,10 +3575,10 @@
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="19"/>
-      <c r="B103" s="20"/>
-      <c r="C103" s="20"/>
-      <c r="D103" s="20"/>
+      <c r="A103" s="20"/>
+      <c r="B103" s="21"/>
+      <c r="C103" s="21"/>
+      <c r="D103" s="21"/>
       <c r="E103" s="12" t="s">
         <v>96</v>
       </c>
@@ -3525,14 +3587,14 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="19"/>
-      <c r="B104" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C104" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D104" s="18" t="s">
+      <c r="A104" s="20"/>
+      <c r="B104" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D104" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E104" s="12" t="s">
@@ -3543,106 +3605,106 @@
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="19"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="16"/>
-      <c r="D105" s="19"/>
+      <c r="A105" s="20"/>
+      <c r="B105" s="20"/>
+      <c r="C105" s="20"/>
+      <c r="D105" s="20"/>
       <c r="E105" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="19"/>
+      <c r="A106" s="20"/>
       <c r="B106" s="20"/>
-      <c r="C106" s="16"/>
+      <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="20"/>
+      <c r="B107" s="21"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F106" s="12" t="s">
+      <c r="F107" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
-      <c r="A107" s="19"/>
-      <c r="B107" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C107" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D107" s="18" t="s">
+    <row r="108" spans="1:6">
+      <c r="A108" s="20"/>
+      <c r="B108" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D108" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E107" s="12" t="s">
+      <c r="E108" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F107" s="12" t="s">
+      <c r="F108" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
-      <c r="A108" s="19"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="16"/>
-      <c r="D108" s="19"/>
-      <c r="E108" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F108" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="19"/>
+      <c r="A109" s="20"/>
       <c r="B109" s="20"/>
-      <c r="C109" s="16"/>
+      <c r="C109" s="22"/>
       <c r="D109" s="20"/>
       <c r="E109" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="20"/>
+      <c r="B110" s="21"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F109" s="12" t="s">
+      <c r="F110" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
-      <c r="A110" s="19"/>
-      <c r="B110" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D110" s="18" t="s">
+    <row r="111" spans="1:6">
+      <c r="A111" s="20"/>
+      <c r="B111" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D111" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E110" s="12" t="s">
+      <c r="E111" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F110" s="12" t="s">
+      <c r="F111" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="A111" s="19"/>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="19"/>
-      <c r="E111" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="19"/>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
+      <c r="A112" s="20"/>
+      <c r="B112" s="20"/>
+      <c r="C112" s="22"/>
+      <c r="D112" s="20"/>
       <c r="E112" s="12" t="s">
         <v>81</v>
       </c>
@@ -3651,10 +3713,10 @@
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="19"/>
-      <c r="B113" s="20"/>
-      <c r="C113" s="20"/>
-      <c r="D113" s="20"/>
+      <c r="A113" s="20"/>
+      <c r="B113" s="21"/>
+      <c r="C113" s="22"/>
+      <c r="D113" s="21"/>
       <c r="E113" s="12" t="s">
         <v>96</v>
       </c>
@@ -3663,14 +3725,14 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="19"/>
-      <c r="B114" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C114" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D114" s="18" t="s">
+      <c r="A114" s="20"/>
+      <c r="B114" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D114" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E114" s="12" t="s">
@@ -3681,10 +3743,10 @@
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="19"/>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-      <c r="D115" s="19"/>
+      <c r="A115" s="20"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="20"/>
       <c r="E115" s="12" t="s">
         <v>80</v>
       </c>
@@ -3693,10 +3755,10 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="19"/>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
-      <c r="D116" s="19"/>
+      <c r="A116" s="20"/>
+      <c r="B116" s="20"/>
+      <c r="C116" s="20"/>
+      <c r="D116" s="20"/>
       <c r="E116" s="12" t="s">
         <v>81</v>
       </c>
@@ -3705,10 +3767,10 @@
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="19"/>
-      <c r="B117" s="20"/>
-      <c r="C117" s="20"/>
-      <c r="D117" s="20"/>
+      <c r="A117" s="20"/>
+      <c r="B117" s="21"/>
+      <c r="C117" s="21"/>
+      <c r="D117" s="21"/>
       <c r="E117" s="12" t="s">
         <v>96</v>
       </c>
@@ -3717,14 +3779,14 @@
       </c>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="19"/>
-      <c r="B118" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D118" s="18" t="s">
+      <c r="A118" s="20"/>
+      <c r="B118" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D118" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E118" s="12" t="s">
@@ -3735,171 +3797,225 @@
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="19"/>
-      <c r="B119" s="19"/>
-      <c r="C119" s="16"/>
-      <c r="D119" s="19"/>
+      <c r="A119" s="20"/>
+      <c r="B119" s="20"/>
+      <c r="C119" s="20"/>
+      <c r="D119" s="20"/>
       <c r="E119" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="19"/>
+      <c r="A120" s="20"/>
       <c r="B120" s="20"/>
-      <c r="C120" s="16"/>
+      <c r="C120" s="20"/>
       <c r="D120" s="20"/>
       <c r="E120" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="20"/>
+      <c r="B121" s="21"/>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F120" s="12" t="s">
+      <c r="F121" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
-      <c r="A121" s="19"/>
-      <c r="B121" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C121" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D121" s="18" t="s">
+    <row r="122" spans="1:6">
+      <c r="A122" s="20"/>
+      <c r="B122" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D122" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E121" s="12" t="s">
+      <c r="E122" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F121" s="12" t="s">
+      <c r="F122" s="12" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" s="19"/>
-      <c r="B122" s="19"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="19"/>
-      <c r="E122" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F122" s="12" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="20"/>
       <c r="B123" s="20"/>
-      <c r="C123" s="16"/>
+      <c r="C123" s="22"/>
       <c r="D123" s="20"/>
       <c r="E123" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="20"/>
+      <c r="B124" s="21"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="21"/>
+      <c r="E124" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F123" s="12" t="s">
+      <c r="F124" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="20"/>
+      <c r="B125" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="20"/>
+      <c r="B126" s="20"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="20"/>
+      <c r="E126" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="21"/>
+      <c r="B127" s="21"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F127" s="12" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="D121:D123"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:A16"/>
+    <mergeCell ref="D3:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C35:C40"/>
+    <mergeCell ref="D35:D40"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="D23:D28"/>
+    <mergeCell ref="C23:C28"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="D29:D34"/>
+    <mergeCell ref="C29:C34"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D56:D60"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="D41:D45"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B41:B45"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="D46:D50"/>
+    <mergeCell ref="B46:B50"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="D68:D71"/>
+    <mergeCell ref="A17:A71"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="D51:D55"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="D83:D85"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="D94:D96"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="A72:A99"/>
+    <mergeCell ref="A100:A127"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="C104:C107"/>
+    <mergeCell ref="D104:D107"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="C111:C113"/>
+    <mergeCell ref="D111:D113"/>
     <mergeCell ref="B114:B117"/>
     <mergeCell ref="C114:C117"/>
     <mergeCell ref="D114:D117"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="A68:A95"/>
-    <mergeCell ref="A96:A123"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="C96:C99"/>
-    <mergeCell ref="D96:D99"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="C100:C103"/>
-    <mergeCell ref="D100:D103"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="D90:D92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C72:C75"/>
-    <mergeCell ref="D72:D75"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="A13:A67"/>
-    <mergeCell ref="D68:D71"/>
-    <mergeCell ref="C68:C71"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="D47:D51"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="D52:D56"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="D31:D36"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="D19:D24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="D25:D30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D13:D18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A3:A12"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="C122:C124"/>
+    <mergeCell ref="D122:D124"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="C125:C127"/>
+    <mergeCell ref="D125:D127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3921,14 +4037,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -3955,50 +4071,50 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="15" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="17"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="18"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="18" t="s">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="8"/>
@@ -4116,7 +4232,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89F3D3C-6CDD-4026-851E-F3F25E51AE26}">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="16.149999999999999"/>
   <cols>
     <col min="1" max="1" width="15.69921875" style="3" customWidth="1"/>
@@ -4130,14 +4246,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -4163,16 +4279,16 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -4183,10 +4299,10 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="19"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="16"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="12" t="s">
         <v>169</v>
       </c>
@@ -4195,10 +4311,10 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="19"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="16"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="12" t="s">
         <v>170</v>
       </c>
@@ -4207,10 +4323,10 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="19"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="17"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="18"/>
       <c r="E6" s="12" t="s">
         <v>171</v>
       </c>
@@ -4219,9 +4335,9 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="19"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="12" t="s">
         <v>15</v>
       </c>
@@ -4233,14 +4349,14 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="19"/>
-      <c r="B8" s="18" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -4251,10 +4367,10 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="12" t="s">
         <v>173</v>
       </c>
@@ -4263,10 +4379,10 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="12" t="s">
         <v>174</v>
       </c>
@@ -4275,9 +4391,9 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="13" t="s">
         <v>15</v>
       </c>
@@ -4289,14 +4405,14 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="19"/>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="12" t="s">
@@ -4307,10 +4423,10 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="16"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
       <c r="E13" s="12" t="s">
         <v>176</v>
       </c>
@@ -4319,10 +4435,10 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="16"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="12" t="s">
         <v>177</v>
       </c>
@@ -4331,10 +4447,10 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="16"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="22"/>
       <c r="E15" s="12" t="s">
         <v>171</v>
       </c>
@@ -4343,10 +4459,10 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="16"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="12" t="s">
         <v>174</v>
       </c>
@@ -4355,9 +4471,9 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="13" t="s">
         <v>15</v>
       </c>
@@ -4369,11 +4485,11 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="19"/>
-      <c r="B18" s="18" t="s">
+      <c r="A18" s="20"/>
+      <c r="B18" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>219</v>
       </c>
       <c r="D18" s="12" t="s">
@@ -4387,9 +4503,9 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="13" t="s">
         <v>15</v>
       </c>
@@ -4401,11 +4517,11 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="19"/>
-      <c r="B20" s="18" t="s">
+      <c r="A20" s="20"/>
+      <c r="B20" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>220</v>
       </c>
       <c r="D20" s="12" t="s">
@@ -4419,10 +4535,10 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="18" t="s">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="19" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -4433,10 +4549,10 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
       <c r="E22" s="12" t="s">
         <v>181</v>
       </c>
@@ -4445,10 +4561,10 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="19"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="12" t="s">
         <v>182</v>
       </c>
@@ -4457,32 +4573,32 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="19"/>
-      <c r="B24" s="18" t="s">
+      <c r="A24" s="20"/>
+      <c r="B24" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="18"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="19"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="19"/>
-      <c r="B26" s="18" t="s">
+      <c r="A26" s="20"/>
+      <c r="B26" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -4493,10 +4609,10 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
       <c r="E27" s="12" t="s">
         <v>183</v>
       </c>
@@ -4505,10 +4621,10 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
       <c r="E28" s="12" t="s">
         <v>184</v>
       </c>
@@ -4517,10 +4633,10 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
       <c r="E29" s="12" t="s">
         <v>171</v>
       </c>
@@ -4529,10 +4645,10 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
       <c r="E30" s="12" t="s">
         <v>174</v>
       </c>
@@ -4541,10 +4657,10 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="18" t="s">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="19" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -4555,10 +4671,10 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="19"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="12" t="s">
         <v>185</v>
       </c>
@@ -4567,14 +4683,14 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="19"/>
-      <c r="B33" s="18" t="s">
+      <c r="A33" s="20"/>
+      <c r="B33" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="16" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -4585,10 +4701,10 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="21"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="16"/>
       <c r="E34" s="12" t="s">
         <v>188</v>
       </c>
@@ -4597,10 +4713,10 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="21"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="16"/>
       <c r="E35" s="12" t="s">
         <v>187</v>
       </c>
@@ -4609,10 +4725,10 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="21"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="16"/>
       <c r="E36" s="12" t="s">
         <v>189</v>
       </c>
@@ -4621,10 +4737,10 @@
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="21"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="16"/>
       <c r="E37" s="12" t="s">
         <v>190</v>
       </c>
@@ -4633,10 +4749,10 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="21"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="16"/>
       <c r="E38" s="12" t="s">
         <v>191</v>
       </c>
@@ -4645,10 +4761,10 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19" t="s">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -4659,10 +4775,10 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="19"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="12" t="s">
         <v>195</v>
       </c>
@@ -4671,14 +4787,14 @@
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="19"/>
-      <c r="B41" s="18" t="s">
+      <c r="A41" s="20"/>
+      <c r="B41" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -4689,10 +4805,10 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
       <c r="E42" s="12" t="s">
         <v>186</v>
       </c>
@@ -4701,10 +4817,10 @@
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
       <c r="E43" s="12" t="s">
         <v>197</v>
       </c>
@@ -4713,10 +4829,10 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
       <c r="E44" s="12" t="s">
         <v>189</v>
       </c>
@@ -4725,10 +4841,10 @@
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
       <c r="E45" s="12" t="s">
         <v>198</v>
       </c>
@@ -4737,10 +4853,10 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
       <c r="E46" s="12" t="s">
         <v>199</v>
       </c>
@@ -4749,10 +4865,10 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="20"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="21"/>
       <c r="E47" s="12" t="s">
         <v>185</v>
       </c>
@@ -4761,10 +4877,10 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="18" t="s">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="19" t="s">
         <v>15</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -4775,10 +4891,10 @@
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="19"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
       <c r="E49" s="12" t="s">
         <v>193</v>
       </c>
@@ -4787,14 +4903,14 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="19"/>
-      <c r="B50" s="18" t="s">
+      <c r="A50" s="20"/>
+      <c r="B50" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -4805,10 +4921,10 @@
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="20"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="12" t="s">
         <v>201</v>
       </c>
@@ -4817,9 +4933,9 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="19"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
       <c r="D52" s="12" t="s">
         <v>15</v>
       </c>
@@ -4831,14 +4947,14 @@
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="19"/>
-      <c r="B53" s="18" t="s">
+      <c r="A53" s="20"/>
+      <c r="B53" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -4849,10 +4965,10 @@
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
       <c r="E54" s="12" t="s">
         <v>203</v>
       </c>
@@ -4861,10 +4977,10 @@
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="20"/>
+      <c r="A55" s="20"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="21"/>
       <c r="E55" s="12" t="s">
         <v>201</v>
       </c>
@@ -4874,8 +4990,8 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="20"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="21"/>
       <c r="D56" s="12" t="s">
         <v>15</v>
       </c>
@@ -4886,33 +5002,93 @@
         <v>11</v>
       </c>
     </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="20"/>
+      <c r="B57" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="C53:C56"/>
-    <mergeCell ref="B53:B56"/>
-    <mergeCell ref="D41:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="C41:C49"/>
-    <mergeCell ref="B41:B49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="D33:D38"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="C33:C40"/>
-    <mergeCell ref="B33:B40"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D26:D30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="C26:C32"/>
-    <mergeCell ref="B26:B32"/>
+  <mergeCells count="40">
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="A3:A61"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:A56"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="B8:B11"/>
@@ -4924,6 +5100,26 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="C20:C23"/>
     <mergeCell ref="B20:B23"/>
+    <mergeCell ref="D33:D38"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="C33:C40"/>
+    <mergeCell ref="B33:B40"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D26:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C26:C32"/>
+    <mergeCell ref="B26:B32"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="D41:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="C41:C49"/>
+    <mergeCell ref="B41:B49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="B50:B52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
